--- a/door_switch_maze/grid/DISRC_nor/episode_rewards_disrc.xlsx
+++ b/door_switch_maze/grid/DISRC_nor/episode_rewards_disrc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B701"/>
+  <dimension ref="A1:B1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.42484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -677,7 +677,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5528124999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -805,7 +805,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>0.5992187499999999</v>
       </c>
     </row>
     <row r="48">
@@ -829,7 +829,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>0.49515625</v>
       </c>
     </row>
     <row r="51">
@@ -869,7 +869,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="56">
@@ -877,7 +877,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>0.1534374999999999</v>
       </c>
     </row>
     <row r="57">
@@ -973,7 +973,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1745312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1221,7 +1221,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>0.28984375</v>
       </c>
     </row>
     <row r="100">
@@ -1229,7 +1229,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>0.2799999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -1317,7 +1317,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>0.2392187499999999</v>
       </c>
     </row>
     <row r="112">
@@ -1389,7 +1389,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="121">
@@ -1397,7 +1397,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>0.2659374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -1405,7 +1405,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>0.5879687499999999</v>
       </c>
     </row>
     <row r="123">
@@ -1453,7 +1453,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>0.13234375</v>
       </c>
     </row>
     <row r="129">
@@ -1461,7 +1461,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>0.5978125</v>
       </c>
     </row>
     <row r="130">
@@ -1485,7 +1485,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>0.17875</v>
       </c>
     </row>
     <row r="133">
@@ -1493,7 +1493,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>0.5992187499999999</v>
       </c>
     </row>
     <row r="134">
@@ -1501,7 +1501,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>0.1520312500000001</v>
       </c>
     </row>
     <row r="135">
@@ -1533,7 +1533,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>0.49515625</v>
       </c>
     </row>
     <row r="139">
@@ -1541,7 +1541,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>0.9015625</v>
       </c>
     </row>
     <row r="140">
@@ -1557,7 +1557,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>0.8284374999999999</v>
       </c>
     </row>
     <row r="142">
@@ -1573,7 +1573,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>0.5795312500000001</v>
       </c>
     </row>
     <row r="144">
@@ -1581,7 +1581,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>0.18578125</v>
       </c>
     </row>
     <row r="145">
@@ -1589,7 +1589,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>0.78625</v>
       </c>
     </row>
     <row r="146">
@@ -1597,7 +1597,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>0.4360937499999999</v>
       </c>
     </row>
     <row r="147">
@@ -1605,7 +1605,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>0.81578125</v>
       </c>
     </row>
     <row r="148">
@@ -1613,7 +1613,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>0.3671875</v>
       </c>
     </row>
     <row r="149">
@@ -1621,7 +1621,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>0.7975</v>
       </c>
     </row>
     <row r="150">
@@ -1629,7 +1629,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>0.4093749999999999</v>
       </c>
     </row>
     <row r="151">
@@ -1637,7 +1637,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>0.34046875</v>
       </c>
     </row>
     <row r="152">
@@ -1645,7 +1645,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>0.1576562500000001</v>
       </c>
     </row>
     <row r="153">
@@ -1653,7 +1653,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>0.1365625</v>
       </c>
     </row>
     <row r="154">
@@ -1677,7 +1677,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>0.42203125</v>
       </c>
     </row>
     <row r="157">
@@ -1701,7 +1701,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>0.34609375</v>
       </c>
     </row>
     <row r="160">
@@ -1725,7 +1725,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>0</v>
+        <v>0.32640625</v>
       </c>
     </row>
     <row r="163">
@@ -1733,7 +1733,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="164">
@@ -1765,7 +1765,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>0.81296875</v>
       </c>
     </row>
     <row r="168">
@@ -1773,7 +1773,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>0.3390624999999999</v>
       </c>
     </row>
     <row r="169">
@@ -1781,7 +1781,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>0.41078125</v>
       </c>
     </row>
     <row r="170">
@@ -1789,7 +1789,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>0.12671875</v>
+        <v>0.31234375</v>
       </c>
     </row>
     <row r="171">
@@ -1821,7 +1821,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>0.6737500000000001</v>
       </c>
     </row>
     <row r="175">
@@ -1869,7 +1869,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>0.3475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -1885,7 +1885,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>0.4360937499999999</v>
       </c>
     </row>
     <row r="183">
@@ -1901,7 +1901,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>0.4445312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -1941,7 +1941,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>0.341875</v>
       </c>
     </row>
     <row r="190">
@@ -1965,7 +1965,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>0.5289062499999999</v>
+        <v>0.1182812499999999</v>
       </c>
     </row>
     <row r="193">
@@ -2005,7 +2005,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>0.4178125</v>
       </c>
     </row>
     <row r="198">
@@ -2013,7 +2013,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>0.1084375</v>
       </c>
     </row>
     <row r="199">
@@ -2053,7 +2053,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>0.45296875</v>
       </c>
     </row>
     <row r="204">
@@ -2077,7 +2077,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>0.724375</v>
       </c>
     </row>
     <row r="207">
@@ -2085,7 +2085,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>0.6371875</v>
       </c>
     </row>
     <row r="208">
@@ -2093,7 +2093,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>0.926875</v>
       </c>
     </row>
     <row r="209">
@@ -2101,7 +2101,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>0</v>
+        <v>0.95359375</v>
       </c>
     </row>
     <row r="210">
@@ -2117,7 +2117,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>0</v>
+        <v>0.6385937500000001</v>
       </c>
     </row>
     <row r="212">
@@ -2125,7 +2125,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>0</v>
+        <v>0.488125</v>
       </c>
     </row>
     <row r="213">
@@ -2133,7 +2133,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>0.803125</v>
       </c>
     </row>
     <row r="214">
@@ -2141,7 +2141,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>0.5246875</v>
       </c>
     </row>
     <row r="215">
@@ -2149,7 +2149,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>0.3503124999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -2157,7 +2157,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>0.7946875</v>
       </c>
     </row>
     <row r="217">
@@ -2165,7 +2165,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>0.4009374999999999</v>
       </c>
     </row>
     <row r="218">
@@ -2181,7 +2181,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="220">
@@ -2189,7 +2189,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>0.5992187499999999</v>
       </c>
     </row>
     <row r="221">
@@ -2197,7 +2197,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>0.7975</v>
       </c>
     </row>
     <row r="222">
@@ -2205,7 +2205,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>0.34046875</v>
       </c>
     </row>
     <row r="223">
@@ -2237,7 +2237,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>0.47265625</v>
       </c>
     </row>
     <row r="227">
@@ -2245,7 +2245,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>0</v>
+        <v>0.780625</v>
       </c>
     </row>
     <row r="228">
@@ -2253,7 +2253,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>0.8396875</v>
       </c>
     </row>
     <row r="229">
@@ -2261,7 +2261,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>0</v>
+        <v>0.5767187499999999</v>
       </c>
     </row>
     <row r="230">
@@ -2269,7 +2269,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>0.91984375</v>
       </c>
     </row>
     <row r="231">
@@ -2277,7 +2277,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>0</v>
+        <v>0.8509375</v>
       </c>
     </row>
     <row r="232">
@@ -2285,7 +2285,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>0</v>
+        <v>0.8509375</v>
       </c>
     </row>
     <row r="233">
@@ -2293,7 +2293,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>0</v>
+        <v>0.938125</v>
       </c>
     </row>
     <row r="234">
@@ -2301,7 +2301,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>0</v>
+        <v>0.94796875</v>
       </c>
     </row>
     <row r="235">
@@ -2309,7 +2309,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>0</v>
+        <v>0.5303125</v>
       </c>
     </row>
     <row r="236">
@@ -2317,7 +2317,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>0.6596875</v>
       </c>
     </row>
     <row r="237">
@@ -2325,7 +2325,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>0</v>
+        <v>0.80734375</v>
       </c>
     </row>
     <row r="238">
@@ -2341,7 +2341,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>0.5457812500000001</v>
       </c>
     </row>
     <row r="240">
@@ -2349,7 +2349,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>0.6737500000000001</v>
       </c>
     </row>
     <row r="241">
@@ -2357,7 +2357,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>0.8987499999999999</v>
       </c>
     </row>
     <row r="242">
@@ -2365,7 +2365,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>0.3503124999999999</v>
+        <v>0.90578125</v>
       </c>
     </row>
     <row r="243">
@@ -2389,7 +2389,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="246">
@@ -2397,7 +2397,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>0.94234375</v>
       </c>
     </row>
     <row r="247">
@@ -2405,7 +2405,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>0.88328125</v>
       </c>
     </row>
     <row r="248">
@@ -2413,7 +2413,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>0.84109375</v>
       </c>
     </row>
     <row r="249">
@@ -2421,7 +2421,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>0.8495312500000001</v>
       </c>
     </row>
     <row r="250">
@@ -2429,7 +2429,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>0</v>
+        <v>0.62171875</v>
       </c>
     </row>
     <row r="251">
@@ -2453,7 +2453,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>0.7229687499999999</v>
       </c>
     </row>
     <row r="254">
@@ -2461,7 +2461,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>0</v>
+        <v>0.91984375</v>
       </c>
     </row>
     <row r="255">
@@ -2477,7 +2477,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>0.8143750000000001</v>
       </c>
     </row>
     <row r="257">
@@ -2485,7 +2485,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>0</v>
+        <v>0.89453125</v>
       </c>
     </row>
     <row r="258">
@@ -2509,7 +2509,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="261">
@@ -2517,7 +2517,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>0</v>
+        <v>0.88890625</v>
       </c>
     </row>
     <row r="262">
@@ -2525,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>0.4403125</v>
+        <v>0.60765625</v>
       </c>
     </row>
     <row r="263">
@@ -2533,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="n">
-        <v>0</v>
+        <v>0.68640625</v>
       </c>
     </row>
     <row r="264">
@@ -2557,7 +2557,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>0.9409375</v>
       </c>
     </row>
     <row r="267">
@@ -2565,7 +2565,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>0.96484375</v>
       </c>
     </row>
     <row r="268">
@@ -2581,7 +2581,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>0.9071875</v>
       </c>
     </row>
     <row r="270">
@@ -2589,7 +2589,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>0.7454687499999999</v>
       </c>
     </row>
     <row r="271">
@@ -2597,7 +2597,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>0.9015625</v>
       </c>
     </row>
     <row r="272">
@@ -2613,7 +2613,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>0</v>
+        <v>0.9128125</v>
       </c>
     </row>
     <row r="274">
@@ -2621,7 +2621,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="n">
-        <v>0</v>
+        <v>0.89171875</v>
       </c>
     </row>
     <row r="275">
@@ -2645,7 +2645,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>0.803125</v>
       </c>
     </row>
     <row r="278">
@@ -2661,7 +2661,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>0.7229687499999999</v>
       </c>
     </row>
     <row r="280">
@@ -2677,7 +2677,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>0</v>
+        <v>0.8607812500000001</v>
       </c>
     </row>
     <row r="282">
@@ -2685,7 +2685,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>0.55140625</v>
       </c>
     </row>
     <row r="283">
@@ -2701,7 +2701,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>0</v>
+        <v>0.9015625</v>
       </c>
     </row>
     <row r="285">
@@ -2709,7 +2709,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="n">
-        <v>0</v>
+        <v>0.93671875</v>
       </c>
     </row>
     <row r="286">
@@ -2717,7 +2717,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>0.2828125</v>
       </c>
     </row>
     <row r="287">
@@ -2725,7 +2725,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>0.10984375</v>
+        <v>0.701875</v>
       </c>
     </row>
     <row r="288">
@@ -2741,7 +2741,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="290">
@@ -2749,7 +2749,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>0.16609375</v>
       </c>
     </row>
     <row r="291">
@@ -2757,7 +2757,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>0.87765625</v>
       </c>
     </row>
     <row r="292">
@@ -2773,7 +2773,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="294">
@@ -2789,7 +2789,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>0.3784375</v>
       </c>
     </row>
     <row r="296">
@@ -2805,7 +2805,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>0.3109375</v>
       </c>
     </row>
     <row r="298">
@@ -2813,7 +2813,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0</v>
+        <v>0.6203125</v>
       </c>
     </row>
     <row r="299">
@@ -2821,7 +2821,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>0</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="300">
@@ -2829,7 +2829,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>0.5992187499999999</v>
       </c>
     </row>
     <row r="301">
@@ -2837,7 +2837,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>0</v>
+        <v>0.8495312500000001</v>
       </c>
     </row>
     <row r="302">
@@ -2845,7 +2845,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>0</v>
+        <v>0.8692187499999999</v>
       </c>
     </row>
     <row r="303">
@@ -2853,7 +2853,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="n">
-        <v>0</v>
+        <v>0.9521875</v>
       </c>
     </row>
     <row r="304">
@@ -2861,7 +2861,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="305">
@@ -2877,7 +2877,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>0.7285937499999999</v>
       </c>
     </row>
     <row r="307">
@@ -2885,7 +2885,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="n">
-        <v>0</v>
+        <v>0.36015625</v>
       </c>
     </row>
     <row r="308">
@@ -2901,7 +2901,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>0</v>
+        <v>0.6934374999999999</v>
       </c>
     </row>
     <row r="310">
@@ -2909,7 +2909,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>0</v>
+        <v>0.701875</v>
       </c>
     </row>
     <row r="311">
@@ -2917,7 +2917,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>0.5879687499999999</v>
       </c>
     </row>
     <row r="312">
@@ -2941,7 +2941,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>0.926875</v>
       </c>
     </row>
     <row r="315">
@@ -2949,7 +2949,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>0.74265625</v>
       </c>
     </row>
     <row r="316">
@@ -2957,7 +2957,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>0.8256250000000001</v>
       </c>
     </row>
     <row r="317">
@@ -2965,7 +2965,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>0.76515625</v>
       </c>
     </row>
     <row r="318">
@@ -2973,7 +2973,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>0.4698437499999999</v>
       </c>
     </row>
     <row r="319">
@@ -2981,7 +2981,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>0.8987499999999999</v>
       </c>
     </row>
     <row r="320">
@@ -2989,7 +2989,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>0.91140625</v>
       </c>
     </row>
     <row r="321">
@@ -2997,7 +2997,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -3005,7 +3005,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>0.31796875</v>
+        <v>0.836875</v>
       </c>
     </row>
     <row r="323">
@@ -3013,7 +3013,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="n">
-        <v>0</v>
+        <v>0.2153125</v>
       </c>
     </row>
     <row r="324">
@@ -3021,7 +3021,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="n">
-        <v>0.69484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -3029,7 +3029,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>0.5682812500000001</v>
+        <v>0.38828125</v>
       </c>
     </row>
     <row r="326">
@@ -3037,7 +3037,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="n">
-        <v>0</v>
+        <v>0.9071875</v>
       </c>
     </row>
     <row r="327">
@@ -3045,7 +3045,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="n">
-        <v>0.1928125000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -3053,7 +3053,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="329">
@@ -3061,7 +3061,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
-        <v>0</v>
+        <v>0.7609375</v>
       </c>
     </row>
     <row r="330">
@@ -3069,7 +3069,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>0</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="331">
@@ -3093,7 +3093,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>0.870625</v>
       </c>
     </row>
     <row r="334">
@@ -3101,7 +3101,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>0.96765625</v>
       </c>
     </row>
     <row r="335">
@@ -3125,7 +3125,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="n">
-        <v>0.5106250000000001</v>
+        <v>0.949375</v>
       </c>
     </row>
     <row r="338">
@@ -3133,7 +3133,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="n">
-        <v>0.54296875</v>
+        <v>0.81015625</v>
       </c>
     </row>
     <row r="339">
@@ -3141,7 +3141,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="n">
-        <v>0</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="340">
@@ -3149,7 +3149,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>0</v>
+        <v>0.7876562499999999</v>
       </c>
     </row>
     <row r="341">
@@ -3157,7 +3157,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="n">
-        <v>0</v>
+        <v>0.8734375</v>
       </c>
     </row>
     <row r="342">
@@ -3165,7 +3165,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>0</v>
+        <v>0.3629687500000001</v>
       </c>
     </row>
     <row r="343">
@@ -3181,7 +3181,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="n">
-        <v>0</v>
+        <v>0.8959375000000001</v>
       </c>
     </row>
     <row r="345">
@@ -3197,7 +3197,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="n">
-        <v>0</v>
+        <v>0.80453125</v>
       </c>
     </row>
     <row r="347">
@@ -3205,7 +3205,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>0</v>
+        <v>0.91703125</v>
       </c>
     </row>
     <row r="348">
@@ -3213,7 +3213,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="n">
-        <v>0</v>
+        <v>0.6653125</v>
       </c>
     </row>
     <row r="349">
@@ -3221,7 +3221,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="n">
-        <v>0</v>
+        <v>0.7229687499999999</v>
       </c>
     </row>
     <row r="350">
@@ -3229,7 +3229,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="n">
-        <v>0</v>
+        <v>0.4332812500000001</v>
       </c>
     </row>
     <row r="351">
@@ -3237,7 +3237,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="n">
-        <v>0</v>
+        <v>0.9634374999999999</v>
       </c>
     </row>
     <row r="352">
@@ -3261,7 +3261,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="n">
-        <v>0.88609375</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="355">
@@ -3269,7 +3269,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="n">
-        <v>0</v>
+        <v>0.7173437499999999</v>
       </c>
     </row>
     <row r="356">
@@ -3277,7 +3277,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="n">
-        <v>0</v>
+        <v>0.746875</v>
       </c>
     </row>
     <row r="357">
@@ -3293,7 +3293,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="359">
@@ -3301,7 +3301,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="n">
-        <v>0</v>
+        <v>0.7496875000000001</v>
       </c>
     </row>
     <row r="360">
@@ -3309,7 +3309,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="n">
-        <v>0</v>
+        <v>0.9240625</v>
       </c>
     </row>
     <row r="361">
@@ -3317,7 +3317,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="n">
-        <v>0</v>
+        <v>0.780625</v>
       </c>
     </row>
     <row r="362">
@@ -3325,7 +3325,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>0</v>
+        <v>0.8509375</v>
       </c>
     </row>
     <row r="363">
@@ -3333,7 +3333,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="n">
-        <v>0</v>
+        <v>0.78625</v>
       </c>
     </row>
     <row r="364">
@@ -3341,7 +3341,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="n">
-        <v>0</v>
+        <v>0.848125</v>
       </c>
     </row>
     <row r="365">
@@ -3349,7 +3349,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="n">
-        <v>0</v>
+        <v>0.4965625</v>
       </c>
     </row>
     <row r="366">
@@ -3357,7 +3357,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="n">
-        <v>0</v>
+        <v>0.2771875</v>
       </c>
     </row>
     <row r="367">
@@ -3365,7 +3365,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="n">
-        <v>0</v>
+        <v>0.6751562499999999</v>
       </c>
     </row>
     <row r="368">
@@ -3373,7 +3373,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="n">
-        <v>0</v>
+        <v>0.983125</v>
       </c>
     </row>
     <row r="369">
@@ -3389,7 +3389,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="n">
-        <v>0</v>
+        <v>0.62171875</v>
       </c>
     </row>
     <row r="371">
@@ -3397,7 +3397,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>0</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="372">
@@ -3405,7 +3405,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>0</v>
+        <v>0.904375</v>
       </c>
     </row>
     <row r="373">
@@ -3413,7 +3413,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="n">
-        <v>0</v>
+        <v>0.8143750000000001</v>
       </c>
     </row>
     <row r="374">
@@ -3421,7 +3421,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="n">
-        <v>0</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="375">
@@ -3437,7 +3437,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="n">
-        <v>0</v>
+        <v>0.3446874999999999</v>
       </c>
     </row>
     <row r="377">
@@ -3461,7 +3461,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="n">
-        <v>0</v>
+        <v>0.88609375</v>
       </c>
     </row>
     <row r="380">
@@ -3477,7 +3477,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>0</v>
+        <v>0.9353125</v>
       </c>
     </row>
     <row r="382">
@@ -3493,7 +3493,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="n">
-        <v>0</v>
+        <v>0.92265625</v>
       </c>
     </row>
     <row r="384">
@@ -3501,7 +3501,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>0</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="385">
@@ -3509,7 +3509,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="n">
-        <v>0</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="386">
@@ -3541,7 +3541,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>0</v>
+        <v>0.5823437499999999</v>
       </c>
     </row>
     <row r="390">
@@ -3557,7 +3557,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="n">
-        <v>0.2237499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -3565,7 +3565,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="n">
-        <v>0</v>
+        <v>0.92125</v>
       </c>
     </row>
     <row r="393">
@@ -3573,7 +3573,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="n">
-        <v>0</v>
+        <v>0.668125</v>
       </c>
     </row>
     <row r="394">
@@ -3581,7 +3581,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="n">
-        <v>0</v>
+        <v>0.97609375</v>
       </c>
     </row>
     <row r="395">
@@ -3589,7 +3589,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>0.8875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -3597,7 +3597,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>0.1337499999999999</v>
+        <v>0.85515625</v>
       </c>
     </row>
     <row r="397">
@@ -3605,7 +3605,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="n">
-        <v>0.52609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -3613,7 +3613,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>0</v>
+        <v>0.9310937500000001</v>
       </c>
     </row>
     <row r="399">
@@ -3621,7 +3621,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="n">
-        <v>0</v>
+        <v>0.8171875</v>
       </c>
     </row>
     <row r="400">
@@ -3629,7 +3629,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="n">
-        <v>0.55421875</v>
+        <v>0.88890625</v>
       </c>
     </row>
     <row r="401">
@@ -3637,7 +3637,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="n">
-        <v>0.235</v>
+        <v>0.83265625</v>
       </c>
     </row>
     <row r="402">
@@ -3645,7 +3645,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="403">
@@ -3653,7 +3653,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="n">
-        <v>0</v>
+        <v>0.8579687499999999</v>
       </c>
     </row>
     <row r="404">
@@ -3661,7 +3661,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="n">
-        <v>0.7159375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
@@ -3669,7 +3669,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="n">
-        <v>0</v>
+        <v>0.6498437500000001</v>
       </c>
     </row>
     <row r="406">
@@ -3677,7 +3677,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="n">
-        <v>0</v>
+        <v>0.87625</v>
       </c>
     </row>
     <row r="407">
@@ -3701,7 +3701,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="n">
-        <v>0</v>
+        <v>0.91703125</v>
       </c>
     </row>
     <row r="410">
@@ -3709,7 +3709,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="n">
-        <v>0</v>
+        <v>0.9310937500000001</v>
       </c>
     </row>
     <row r="411">
@@ -3717,7 +3717,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="n">
-        <v>0.60625</v>
+        <v>0.7524999999999999</v>
       </c>
     </row>
     <row r="412">
@@ -3725,7 +3725,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="n">
-        <v>0</v>
+        <v>0.48390625</v>
       </c>
     </row>
     <row r="413">
@@ -3733,7 +3733,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="n">
-        <v>0</v>
+        <v>0.75671875</v>
       </c>
     </row>
     <row r="414">
@@ -3741,7 +3741,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="n">
-        <v>0</v>
+        <v>0.55140625</v>
       </c>
     </row>
     <row r="415">
@@ -3749,7 +3749,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="n">
-        <v>0</v>
+        <v>0.848125</v>
       </c>
     </row>
     <row r="416">
@@ -3757,7 +3757,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="n">
-        <v>0</v>
+        <v>0.18296875</v>
       </c>
     </row>
     <row r="417">
@@ -3765,7 +3765,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="n">
-        <v>0</v>
+        <v>0.71171875</v>
       </c>
     </row>
     <row r="418">
@@ -3781,7 +3781,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="n">
-        <v>0</v>
+        <v>0.89453125</v>
       </c>
     </row>
     <row r="420">
@@ -3789,7 +3789,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="421">
@@ -3797,7 +3797,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="n">
-        <v>0</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="422">
@@ -3805,7 +3805,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="n">
-        <v>0.1042187499999999</v>
+        <v>0.48390625</v>
       </c>
     </row>
     <row r="423">
@@ -3821,7 +3821,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="n">
-        <v>0</v>
+        <v>0.40234375</v>
       </c>
     </row>
     <row r="425">
@@ -3829,7 +3829,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="n">
-        <v>0</v>
+        <v>0.83828125</v>
       </c>
     </row>
     <row r="426">
@@ -3845,7 +3845,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="n">
-        <v>0</v>
+        <v>0.7524999999999999</v>
       </c>
     </row>
     <row r="428">
@@ -3853,7 +3853,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="n">
-        <v>0</v>
+        <v>0.89734375</v>
       </c>
     </row>
     <row r="429">
@@ -3877,7 +3877,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="n">
-        <v>0</v>
+        <v>0.32640625</v>
       </c>
     </row>
     <row r="432">
@@ -3885,7 +3885,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="n">
-        <v>0</v>
+        <v>0.81859375</v>
       </c>
     </row>
     <row r="433">
@@ -3909,7 +3909,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="n">
-        <v>0</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="436">
@@ -3917,7 +3917,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="n">
-        <v>0.2799999999999999</v>
+        <v>0.91421875</v>
       </c>
     </row>
     <row r="437">
@@ -3925,7 +3925,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="n">
-        <v>0</v>
+        <v>0.81859375</v>
       </c>
     </row>
     <row r="438">
@@ -3933,7 +3933,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>0.595</v>
+        <v>0.34890625</v>
       </c>
     </row>
     <row r="439">
@@ -3941,7 +3941,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>0</v>
+        <v>0.95078125</v>
       </c>
     </row>
     <row r="440">
@@ -3981,7 +3981,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="445">
@@ -3989,7 +3989,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="n">
-        <v>0</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="446">
@@ -3997,7 +3997,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="n">
-        <v>0</v>
+        <v>0.4796874999999999</v>
       </c>
     </row>
     <row r="447">
@@ -4005,7 +4005,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="n">
-        <v>0.53734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -4013,7 +4013,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="n">
-        <v>0</v>
+        <v>0.465625</v>
       </c>
     </row>
     <row r="449">
@@ -4021,7 +4021,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="n">
-        <v>0.32359375</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="450">
@@ -4029,7 +4029,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="n">
-        <v>0</v>
+        <v>0.7271875</v>
       </c>
     </row>
     <row r="451">
@@ -4037,7 +4037,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="n">
-        <v>0</v>
+        <v>0.91984375</v>
       </c>
     </row>
     <row r="452">
@@ -4045,7 +4045,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="n">
-        <v>0</v>
+        <v>0.83546875</v>
       </c>
     </row>
     <row r="453">
@@ -4053,7 +4053,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="n">
-        <v>0</v>
+        <v>0.724375</v>
       </c>
     </row>
     <row r="454">
@@ -4061,7 +4061,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="n">
-        <v>0</v>
+        <v>0.9339062499999999</v>
       </c>
     </row>
     <row r="455">
@@ -4069,7 +4069,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>0</v>
+        <v>0.51625</v>
       </c>
     </row>
     <row r="456">
@@ -4077,7 +4077,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="n">
-        <v>0</v>
+        <v>0.91421875</v>
       </c>
     </row>
     <row r="457">
@@ -4085,7 +4085,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="n">
-        <v>0</v>
+        <v>0.89171875</v>
       </c>
     </row>
     <row r="458">
@@ -4093,7 +4093,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="n">
-        <v>0</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="459">
@@ -4101,7 +4101,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="n">
-        <v>0</v>
+        <v>0.84109375</v>
       </c>
     </row>
     <row r="460">
@@ -4117,7 +4117,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="n">
-        <v>0.4909374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462">
@@ -4125,7 +4125,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="n">
-        <v>0</v>
+        <v>0.8846875</v>
       </c>
     </row>
     <row r="463">
@@ -4133,7 +4133,7 @@
         <v>462</v>
       </c>
       <c r="B463" t="n">
-        <v>0</v>
+        <v>0.5528124999999999</v>
       </c>
     </row>
     <row r="464">
@@ -4149,7 +4149,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="n">
-        <v>0</v>
+        <v>0.5640624999999999</v>
       </c>
     </row>
     <row r="466">
@@ -4157,7 +4157,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="n">
-        <v>0</v>
+        <v>0.83828125</v>
       </c>
     </row>
     <row r="467">
@@ -4165,7 +4165,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="n">
-        <v>0</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="468">
@@ -4173,7 +4173,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="n">
-        <v>0</v>
+        <v>0.94796875</v>
       </c>
     </row>
     <row r="469">
@@ -4181,7 +4181,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="n">
-        <v>0</v>
+        <v>0.5640624999999999</v>
       </c>
     </row>
     <row r="470">
@@ -4197,7 +4197,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="n">
-        <v>0</v>
+        <v>0.881875</v>
       </c>
     </row>
     <row r="472">
@@ -4205,7 +4205,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="n">
-        <v>0</v>
+        <v>0.85375</v>
       </c>
     </row>
     <row r="473">
@@ -4213,7 +4213,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="n">
-        <v>0</v>
+        <v>0.9310937500000001</v>
       </c>
     </row>
     <row r="474">
@@ -4221,7 +4221,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="475">
@@ -4229,7 +4229,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="n">
-        <v>0</v>
+        <v>0.9409375</v>
       </c>
     </row>
     <row r="476">
@@ -4245,7 +4245,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="n">
-        <v>0</v>
+        <v>0.7665625</v>
       </c>
     </row>
     <row r="478">
@@ -4261,7 +4261,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="n">
-        <v>0</v>
+        <v>0.9803125</v>
       </c>
     </row>
     <row r="480">
@@ -4269,7 +4269,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="n">
-        <v>0</v>
+        <v>0.938125</v>
       </c>
     </row>
     <row r="481">
@@ -4277,7 +4277,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="n">
-        <v>0</v>
+        <v>0.84671875</v>
       </c>
     </row>
     <row r="482">
@@ -4309,7 +4309,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="n">
-        <v>0</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="486">
@@ -4317,7 +4317,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="n">
-        <v>0</v>
+        <v>0.93953125</v>
       </c>
     </row>
     <row r="487">
@@ -4325,7 +4325,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="n">
-        <v>0</v>
+        <v>0.84671875</v>
       </c>
     </row>
     <row r="488">
@@ -4349,7 +4349,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="n">
-        <v>0</v>
+        <v>0.2040624999999999</v>
       </c>
     </row>
     <row r="491">
@@ -4365,7 +4365,7 @@
         <v>491</v>
       </c>
       <c r="B492" t="n">
-        <v>0</v>
+        <v>0.90859375</v>
       </c>
     </row>
     <row r="493">
@@ -4373,7 +4373,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="n">
-        <v>0.61890625</v>
+        <v>0.54859375</v>
       </c>
     </row>
     <row r="494">
@@ -4421,7 +4421,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="n">
-        <v>0</v>
+        <v>0.7089062500000001</v>
       </c>
     </row>
     <row r="500">
@@ -4429,7 +4429,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="n">
-        <v>0</v>
+        <v>0.8959375000000001</v>
       </c>
     </row>
     <row r="501">
@@ -4445,7 +4445,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="n">
-        <v>0</v>
+        <v>0.2884375</v>
       </c>
     </row>
     <row r="503">
@@ -4453,7 +4453,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="n">
-        <v>0</v>
+        <v>0.4684375000000001</v>
       </c>
     </row>
     <row r="504">
@@ -4469,7 +4469,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="n">
-        <v>0</v>
+        <v>0.6034375000000001</v>
       </c>
     </row>
     <row r="506">
@@ -4501,7 +4501,7 @@
         <v>508</v>
       </c>
       <c r="B509" t="n">
-        <v>0.18015625</v>
+        <v>0.87765625</v>
       </c>
     </row>
     <row r="510">
@@ -4509,7 +4509,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="n">
-        <v>0</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="511">
@@ -4541,7 +4541,7 @@
         <v>513</v>
       </c>
       <c r="B514" t="n">
-        <v>0.12109375</v>
+        <v>0.926875</v>
       </c>
     </row>
     <row r="515">
@@ -4549,7 +4549,7 @@
         <v>514</v>
       </c>
       <c r="B515" t="n">
-        <v>0.3840625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516">
@@ -4557,7 +4557,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="n">
-        <v>0</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="517">
@@ -4565,7 +4565,7 @@
         <v>516</v>
       </c>
       <c r="B517" t="n">
-        <v>0</v>
+        <v>0.66390625</v>
       </c>
     </row>
     <row r="518">
@@ -4573,7 +4573,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="n">
-        <v>0</v>
+        <v>0.7089062500000001</v>
       </c>
     </row>
     <row r="519">
@@ -4581,7 +4581,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="520">
@@ -4597,7 +4597,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="n">
-        <v>0</v>
+        <v>0.1548437499999999</v>
       </c>
     </row>
     <row r="522">
@@ -4605,7 +4605,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="n">
-        <v>0.34046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523">
@@ -4621,7 +4621,7 @@
         <v>523</v>
       </c>
       <c r="B524" t="n">
-        <v>0</v>
+        <v>0.7975</v>
       </c>
     </row>
     <row r="525">
@@ -4629,7 +4629,7 @@
         <v>524</v>
       </c>
       <c r="B525" t="n">
-        <v>0</v>
+        <v>0.91140625</v>
       </c>
     </row>
     <row r="526">
@@ -4645,7 +4645,7 @@
         <v>526</v>
       </c>
       <c r="B527" t="n">
-        <v>0</v>
+        <v>0.6118749999999999</v>
       </c>
     </row>
     <row r="528">
@@ -4661,7 +4661,7 @@
         <v>528</v>
       </c>
       <c r="B529" t="n">
-        <v>0</v>
+        <v>0.34890625</v>
       </c>
     </row>
     <row r="530">
@@ -4669,7 +4669,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="n">
-        <v>0</v>
+        <v>0.70609375</v>
       </c>
     </row>
     <row r="531">
@@ -4693,7 +4693,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="n">
-        <v>0</v>
+        <v>0.83265625</v>
       </c>
     </row>
     <row r="534">
@@ -4701,7 +4701,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="n">
-        <v>0</v>
+        <v>0.8635937499999999</v>
       </c>
     </row>
     <row r="535">
@@ -4717,7 +4717,7 @@
         <v>535</v>
       </c>
       <c r="B536" t="n">
-        <v>0</v>
+        <v>0.915625</v>
       </c>
     </row>
     <row r="537">
@@ -4733,7 +4733,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="n">
-        <v>0</v>
+        <v>0.7159375</v>
       </c>
     </row>
     <row r="539">
@@ -4741,7 +4741,7 @@
         <v>538</v>
       </c>
       <c r="B539" t="n">
-        <v>0</v>
+        <v>0.8959375000000001</v>
       </c>
     </row>
     <row r="540">
@@ -4749,7 +4749,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="n">
-        <v>0.6118749999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="541">
@@ -4757,7 +4757,7 @@
         <v>540</v>
       </c>
       <c r="B541" t="n">
-        <v>0</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="542">
@@ -4765,7 +4765,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="n">
-        <v>0</v>
+        <v>0.79609375</v>
       </c>
     </row>
     <row r="543">
@@ -4773,7 +4773,7 @@
         <v>542</v>
       </c>
       <c r="B543" t="n">
-        <v>0.47265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544">
@@ -4781,7 +4781,7 @@
         <v>543</v>
       </c>
       <c r="B544" t="n">
-        <v>0.5921875</v>
+        <v>0.6118749999999999</v>
       </c>
     </row>
     <row r="545">
@@ -4789,7 +4789,7 @@
         <v>544</v>
       </c>
       <c r="B545" t="n">
-        <v>0</v>
+        <v>0.82421875</v>
       </c>
     </row>
     <row r="546">
@@ -4797,7 +4797,7 @@
         <v>545</v>
       </c>
       <c r="B546" t="n">
-        <v>0</v>
+        <v>0.5696874999999999</v>
       </c>
     </row>
     <row r="547">
@@ -4805,7 +4805,7 @@
         <v>546</v>
       </c>
       <c r="B547" t="n">
-        <v>0</v>
+        <v>0.8284374999999999</v>
       </c>
     </row>
     <row r="548">
@@ -4821,7 +4821,7 @@
         <v>548</v>
       </c>
       <c r="B549" t="n">
-        <v>0.19140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="550">
@@ -4837,7 +4837,7 @@
         <v>550</v>
       </c>
       <c r="B551" t="n">
-        <v>0</v>
+        <v>0.5879687499999999</v>
       </c>
     </row>
     <row r="552">
@@ -4877,7 +4877,7 @@
         <v>555</v>
       </c>
       <c r="B556" t="n">
-        <v>0</v>
+        <v>0.82140625</v>
       </c>
     </row>
     <row r="557">
@@ -4885,7 +4885,7 @@
         <v>556</v>
       </c>
       <c r="B557" t="n">
-        <v>0</v>
+        <v>0.926875</v>
       </c>
     </row>
     <row r="558">
@@ -4893,7 +4893,7 @@
         <v>557</v>
       </c>
       <c r="B558" t="n">
-        <v>0</v>
+        <v>0.8987499999999999</v>
       </c>
     </row>
     <row r="559">
@@ -4909,7 +4909,7 @@
         <v>559</v>
       </c>
       <c r="B560" t="n">
-        <v>0</v>
+        <v>0.9282812499999999</v>
       </c>
     </row>
     <row r="561">
@@ -4917,7 +4917,7 @@
         <v>560</v>
       </c>
       <c r="B561" t="n">
-        <v>0</v>
+        <v>0.690625</v>
       </c>
     </row>
     <row r="562">
@@ -4925,7 +4925,7 @@
         <v>561</v>
       </c>
       <c r="B562" t="n">
-        <v>0</v>
+        <v>0.69625</v>
       </c>
     </row>
     <row r="563">
@@ -4933,7 +4933,7 @@
         <v>562</v>
       </c>
       <c r="B563" t="n">
-        <v>0</v>
+        <v>0.78484375</v>
       </c>
     </row>
     <row r="564">
@@ -4941,7 +4941,7 @@
         <v>563</v>
       </c>
       <c r="B564" t="n">
-        <v>0</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="565">
@@ -4957,7 +4957,7 @@
         <v>565</v>
       </c>
       <c r="B566" t="n">
-        <v>0.28140625</v>
+        <v>0.983125</v>
       </c>
     </row>
     <row r="567">
@@ -4965,7 +4965,7 @@
         <v>566</v>
       </c>
       <c r="B567" t="n">
-        <v>0</v>
+        <v>0.91984375</v>
       </c>
     </row>
     <row r="568">
@@ -4973,7 +4973,7 @@
         <v>567</v>
       </c>
       <c r="B568" t="n">
-        <v>0</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="569">
@@ -4981,7 +4981,7 @@
         <v>568</v>
       </c>
       <c r="B569" t="n">
-        <v>0</v>
+        <v>0.7496875000000001</v>
       </c>
     </row>
     <row r="570">
@@ -5013,7 +5013,7 @@
         <v>572</v>
       </c>
       <c r="B573" t="n">
-        <v>0</v>
+        <v>0.7778125</v>
       </c>
     </row>
     <row r="574">
@@ -5021,7 +5021,7 @@
         <v>573</v>
       </c>
       <c r="B574" t="n">
-        <v>0.68359375</v>
+        <v>0.803125</v>
       </c>
     </row>
     <row r="575">
@@ -5029,7 +5029,7 @@
         <v>574</v>
       </c>
       <c r="B575" t="n">
-        <v>0</v>
+        <v>0.8790625</v>
       </c>
     </row>
     <row r="576">
@@ -5037,7 +5037,7 @@
         <v>575</v>
       </c>
       <c r="B576" t="n">
-        <v>0</v>
+        <v>0.25328125</v>
       </c>
     </row>
     <row r="577">
@@ -5053,7 +5053,7 @@
         <v>577</v>
       </c>
       <c r="B578" t="n">
-        <v>0</v>
+        <v>0.66390625</v>
       </c>
     </row>
     <row r="579">
@@ -5061,7 +5061,7 @@
         <v>578</v>
       </c>
       <c r="B579" t="n">
-        <v>0</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="580">
@@ -5125,7 +5125,7 @@
         <v>586</v>
       </c>
       <c r="B587" t="n">
-        <v>0</v>
+        <v>0.66109375</v>
       </c>
     </row>
     <row r="588">
@@ -5133,7 +5133,7 @@
         <v>587</v>
       </c>
       <c r="B588" t="n">
-        <v>0.1520312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="589">
@@ -5149,7 +5149,7 @@
         <v>589</v>
       </c>
       <c r="B590" t="n">
-        <v>0</v>
+        <v>0.1632812499999999</v>
       </c>
     </row>
     <row r="591">
@@ -5157,7 +5157,7 @@
         <v>590</v>
       </c>
       <c r="B591" t="n">
-        <v>0</v>
+        <v>0.73421875</v>
       </c>
     </row>
     <row r="592">
@@ -5189,7 +5189,7 @@
         <v>594</v>
       </c>
       <c r="B595" t="n">
-        <v>0</v>
+        <v>0.713125</v>
       </c>
     </row>
     <row r="596">
@@ -5197,7 +5197,7 @@
         <v>595</v>
       </c>
       <c r="B596" t="n">
-        <v>0</v>
+        <v>0.3953125</v>
       </c>
     </row>
     <row r="597">
@@ -5205,7 +5205,7 @@
         <v>596</v>
       </c>
       <c r="B597" t="n">
-        <v>0</v>
+        <v>0.915625</v>
       </c>
     </row>
     <row r="598">
@@ -5213,7 +5213,7 @@
         <v>597</v>
       </c>
       <c r="B598" t="n">
-        <v>0.6146875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="599">
@@ -5229,7 +5229,7 @@
         <v>599</v>
       </c>
       <c r="B600" t="n">
-        <v>0.3095312499999999</v>
+        <v>0.8692187499999999</v>
       </c>
     </row>
     <row r="601">
@@ -5245,7 +5245,7 @@
         <v>601</v>
       </c>
       <c r="B602" t="n">
-        <v>0</v>
+        <v>0.82984375</v>
       </c>
     </row>
     <row r="603">
@@ -5253,7 +5253,7 @@
         <v>602</v>
       </c>
       <c r="B603" t="n">
-        <v>0</v>
+        <v>0.555625</v>
       </c>
     </row>
     <row r="604">
@@ -5269,7 +5269,7 @@
         <v>604</v>
       </c>
       <c r="B605" t="n">
-        <v>0</v>
+        <v>0.7215625</v>
       </c>
     </row>
     <row r="606">
@@ -5277,7 +5277,7 @@
         <v>605</v>
       </c>
       <c r="B606" t="n">
-        <v>0</v>
+        <v>0.656875</v>
       </c>
     </row>
     <row r="607">
@@ -5285,7 +5285,7 @@
         <v>606</v>
       </c>
       <c r="B607" t="n">
-        <v>0</v>
+        <v>0.9353125</v>
       </c>
     </row>
     <row r="608">
@@ -5317,7 +5317,7 @@
         <v>610</v>
       </c>
       <c r="B611" t="n">
-        <v>0.6484375</v>
+        <v>0.89453125</v>
       </c>
     </row>
     <row r="612">
@@ -5325,7 +5325,7 @@
         <v>611</v>
       </c>
       <c r="B612" t="n">
-        <v>0</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="613">
@@ -5333,7 +5333,7 @@
         <v>612</v>
       </c>
       <c r="B613" t="n">
-        <v>0</v>
+        <v>0.82703125</v>
       </c>
     </row>
     <row r="614">
@@ -5341,7 +5341,7 @@
         <v>613</v>
       </c>
       <c r="B614" t="n">
-        <v>0.29125</v>
+        <v>0.78625</v>
       </c>
     </row>
     <row r="615">
@@ -5349,7 +5349,7 @@
         <v>614</v>
       </c>
       <c r="B615" t="n">
-        <v>0</v>
+        <v>0.97609375</v>
       </c>
     </row>
     <row r="616">
@@ -5357,7 +5357,7 @@
         <v>615</v>
       </c>
       <c r="B616" t="n">
-        <v>0</v>
+        <v>0.9409375</v>
       </c>
     </row>
     <row r="617">
@@ -5365,7 +5365,7 @@
         <v>616</v>
       </c>
       <c r="B617" t="n">
-        <v>0</v>
+        <v>0.91703125</v>
       </c>
     </row>
     <row r="618">
@@ -5373,7 +5373,7 @@
         <v>617</v>
       </c>
       <c r="B618" t="n">
-        <v>0</v>
+        <v>0.9310937500000001</v>
       </c>
     </row>
     <row r="619">
@@ -5381,7 +5381,7 @@
         <v>618</v>
       </c>
       <c r="B619" t="n">
-        <v>0</v>
+        <v>0.5092187500000001</v>
       </c>
     </row>
     <row r="620">
@@ -5405,7 +5405,7 @@
         <v>621</v>
       </c>
       <c r="B622" t="n">
-        <v>0</v>
+        <v>0.6695312499999999</v>
       </c>
     </row>
     <row r="623">
@@ -5413,7 +5413,7 @@
         <v>622</v>
       </c>
       <c r="B623" t="n">
-        <v>0.68640625</v>
+        <v>0.91703125</v>
       </c>
     </row>
     <row r="624">
@@ -5421,7 +5421,7 @@
         <v>623</v>
       </c>
       <c r="B624" t="n">
-        <v>0</v>
+        <v>0.7581249999999999</v>
       </c>
     </row>
     <row r="625">
@@ -5445,7 +5445,7 @@
         <v>626</v>
       </c>
       <c r="B627" t="n">
-        <v>0</v>
+        <v>0.735625</v>
       </c>
     </row>
     <row r="628">
@@ -5453,7 +5453,7 @@
         <v>627</v>
       </c>
       <c r="B628" t="n">
-        <v>0</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="629">
@@ -5469,7 +5469,7 @@
         <v>629</v>
       </c>
       <c r="B630" t="n">
-        <v>0</v>
+        <v>0.87765625</v>
       </c>
     </row>
     <row r="631">
@@ -5477,7 +5477,7 @@
         <v>630</v>
       </c>
       <c r="B631" t="n">
-        <v>0</v>
+        <v>0.95078125</v>
       </c>
     </row>
     <row r="632">
@@ -5485,7 +5485,7 @@
         <v>631</v>
       </c>
       <c r="B632" t="n">
-        <v>0</v>
+        <v>0.701875</v>
       </c>
     </row>
     <row r="633">
@@ -5501,7 +5501,7 @@
         <v>633</v>
       </c>
       <c r="B634" t="n">
-        <v>0</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="635">
@@ -5517,7 +5517,7 @@
         <v>635</v>
       </c>
       <c r="B636" t="n">
-        <v>0</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="637">
@@ -5525,7 +5525,7 @@
         <v>636</v>
       </c>
       <c r="B637" t="n">
-        <v>0</v>
+        <v>0.96203125</v>
       </c>
     </row>
     <row r="638">
@@ -5541,7 +5541,7 @@
         <v>638</v>
       </c>
       <c r="B639" t="n">
-        <v>0</v>
+        <v>0.92125</v>
       </c>
     </row>
     <row r="640">
@@ -5549,7 +5549,7 @@
         <v>639</v>
       </c>
       <c r="B640" t="n">
-        <v>0</v>
+        <v>0.85375</v>
       </c>
     </row>
     <row r="641">
@@ -5565,7 +5565,7 @@
         <v>641</v>
       </c>
       <c r="B642" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="643">
@@ -5573,7 +5573,7 @@
         <v>642</v>
       </c>
       <c r="B643" t="n">
-        <v>0</v>
+        <v>0.9128125</v>
       </c>
     </row>
     <row r="644">
@@ -5581,7 +5581,7 @@
         <v>643</v>
       </c>
       <c r="B644" t="n">
-        <v>0</v>
+        <v>0.19984375</v>
       </c>
     </row>
     <row r="645">
@@ -5613,7 +5613,7 @@
         <v>647</v>
       </c>
       <c r="B648" t="n">
-        <v>0</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="649">
@@ -5629,7 +5629,7 @@
         <v>649</v>
       </c>
       <c r="B650" t="n">
-        <v>0</v>
+        <v>0.93671875</v>
       </c>
     </row>
     <row r="651">
@@ -5645,7 +5645,7 @@
         <v>651</v>
       </c>
       <c r="B652" t="n">
-        <v>0.10140625</v>
+        <v>0.9128125</v>
       </c>
     </row>
     <row r="653">
@@ -5661,7 +5661,7 @@
         <v>653</v>
       </c>
       <c r="B654" t="n">
-        <v>0</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="655">
@@ -5677,7 +5677,7 @@
         <v>655</v>
       </c>
       <c r="B656" t="n">
-        <v>0.18015625</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="657">
@@ -5693,7 +5693,7 @@
         <v>657</v>
       </c>
       <c r="B658" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="659">
@@ -5701,7 +5701,7 @@
         <v>658</v>
       </c>
       <c r="B659" t="n">
-        <v>0</v>
+        <v>0.7553125000000001</v>
       </c>
     </row>
     <row r="660">
@@ -5709,7 +5709,7 @@
         <v>659</v>
       </c>
       <c r="B660" t="n">
-        <v>0</v>
+        <v>0.69484375</v>
       </c>
     </row>
     <row r="661">
@@ -5725,7 +5725,7 @@
         <v>661</v>
       </c>
       <c r="B662" t="n">
-        <v>0</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="663">
@@ -5741,7 +5741,7 @@
         <v>663</v>
       </c>
       <c r="B664" t="n">
-        <v>0.67796875</v>
+        <v>0.6498437500000001</v>
       </c>
     </row>
     <row r="665">
@@ -5757,7 +5757,7 @@
         <v>665</v>
       </c>
       <c r="B666" t="n">
-        <v>0</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="667">
@@ -5765,7 +5765,7 @@
         <v>666</v>
       </c>
       <c r="B667" t="n">
-        <v>0</v>
+        <v>0.8692187499999999</v>
       </c>
     </row>
     <row r="668">
@@ -5773,7 +5773,7 @@
         <v>667</v>
       </c>
       <c r="B668" t="n">
-        <v>0</v>
+        <v>0.75109375</v>
       </c>
     </row>
     <row r="669">
@@ -5781,7 +5781,7 @@
         <v>668</v>
       </c>
       <c r="B669" t="n">
-        <v>0.6737500000000001</v>
+        <v>0.7876562499999999</v>
       </c>
     </row>
     <row r="670">
@@ -5805,7 +5805,7 @@
         <v>671</v>
       </c>
       <c r="B672" t="n">
-        <v>0</v>
+        <v>0.8635937499999999</v>
       </c>
     </row>
     <row r="673">
@@ -5813,7 +5813,7 @@
         <v>672</v>
       </c>
       <c r="B673" t="n">
-        <v>0</v>
+        <v>0.90015625</v>
       </c>
     </row>
     <row r="674">
@@ -5821,7 +5821,7 @@
         <v>673</v>
       </c>
       <c r="B674" t="n">
-        <v>0</v>
+        <v>0.96203125</v>
       </c>
     </row>
     <row r="675">
@@ -5829,7 +5829,7 @@
         <v>674</v>
       </c>
       <c r="B675" t="n">
-        <v>0</v>
+        <v>0.96484375</v>
       </c>
     </row>
     <row r="676">
@@ -5837,7 +5837,7 @@
         <v>675</v>
       </c>
       <c r="B676" t="n">
-        <v>0</v>
+        <v>0.7834375</v>
       </c>
     </row>
     <row r="677">
@@ -5893,7 +5893,7 @@
         <v>682</v>
       </c>
       <c r="B683" t="n">
-        <v>0</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="684">
@@ -5909,7 +5909,7 @@
         <v>684</v>
       </c>
       <c r="B685" t="n">
-        <v>0</v>
+        <v>0.499375</v>
       </c>
     </row>
     <row r="686">
@@ -5917,7 +5917,7 @@
         <v>685</v>
       </c>
       <c r="B686" t="n">
-        <v>0.4571875</v>
+        <v>0.97609375</v>
       </c>
     </row>
     <row r="687">
@@ -5925,7 +5925,7 @@
         <v>686</v>
       </c>
       <c r="B687" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="688">
@@ -5933,7 +5933,7 @@
         <v>687</v>
       </c>
       <c r="B688" t="n">
-        <v>0.57109375</v>
+        <v>0.9339062499999999</v>
       </c>
     </row>
     <row r="689">
@@ -5941,7 +5941,7 @@
         <v>688</v>
       </c>
       <c r="B689" t="n">
-        <v>0</v>
+        <v>0.63296875</v>
       </c>
     </row>
     <row r="690">
@@ -5973,7 +5973,7 @@
         <v>692</v>
       </c>
       <c r="B693" t="n">
-        <v>0</v>
+        <v>0.87625</v>
       </c>
     </row>
     <row r="694">
@@ -5981,7 +5981,7 @@
         <v>693</v>
       </c>
       <c r="B694" t="n">
-        <v>0</v>
+        <v>0.8987499999999999</v>
       </c>
     </row>
     <row r="695">
@@ -5989,7 +5989,7 @@
         <v>694</v>
       </c>
       <c r="B695" t="n">
-        <v>0.4065624999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="696">
@@ -5997,7 +5997,7 @@
         <v>695</v>
       </c>
       <c r="B696" t="n">
-        <v>0</v>
+        <v>0.5387500000000001</v>
       </c>
     </row>
     <row r="697">
@@ -6013,7 +6013,7 @@
         <v>697</v>
       </c>
       <c r="B698" t="n">
-        <v>0</v>
+        <v>0.9746875</v>
       </c>
     </row>
     <row r="699">
@@ -6029,7 +6029,7 @@
         <v>699</v>
       </c>
       <c r="B700" t="n">
-        <v>0</v>
+        <v>0.55140625</v>
       </c>
     </row>
     <row r="701">
@@ -6037,6 +6037,2406 @@
         <v>700</v>
       </c>
       <c r="B701" t="n">
+        <v>0.88609375</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>701</v>
+      </c>
+      <c r="B702" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>702</v>
+      </c>
+      <c r="B703" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>703</v>
+      </c>
+      <c r="B704" t="n">
+        <v>0.7890625</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>704</v>
+      </c>
+      <c r="B705" t="n">
+        <v>0.960625</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>705</v>
+      </c>
+      <c r="B706" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>706</v>
+      </c>
+      <c r="B707" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>707</v>
+      </c>
+      <c r="B708" t="n">
+        <v>0.859375</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>708</v>
+      </c>
+      <c r="B709" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>709</v>
+      </c>
+      <c r="B710" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>710</v>
+      </c>
+      <c r="B711" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>711</v>
+      </c>
+      <c r="B712" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>712</v>
+      </c>
+      <c r="B713" t="n">
+        <v>0.6751562499999999</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>713</v>
+      </c>
+      <c r="B714" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>714</v>
+      </c>
+      <c r="B715" t="n">
+        <v>0.95359375</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>715</v>
+      </c>
+      <c r="B716" t="n">
+        <v>0.870625</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>716</v>
+      </c>
+      <c r="B717" t="n">
+        <v>0.926875</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>717</v>
+      </c>
+      <c r="B718" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>718</v>
+      </c>
+      <c r="B719" t="n">
+        <v>0.9803125</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>719</v>
+      </c>
+      <c r="B720" t="n">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>720</v>
+      </c>
+      <c r="B721" t="n">
+        <v>0.56125</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>721</v>
+      </c>
+      <c r="B722" t="n">
+        <v>0.8903125000000001</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>722</v>
+      </c>
+      <c r="B723" t="n">
+        <v>0.9240625</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>723</v>
+      </c>
+      <c r="B724" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>724</v>
+      </c>
+      <c r="B725" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>725</v>
+      </c>
+      <c r="B726" t="n">
+        <v>0.8931249999999999</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>726</v>
+      </c>
+      <c r="B727" t="n">
+        <v>0.955</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>727</v>
+      </c>
+      <c r="B728" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>728</v>
+      </c>
+      <c r="B729" t="n">
+        <v>0.92265625</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>729</v>
+      </c>
+      <c r="B730" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>730</v>
+      </c>
+      <c r="B731" t="n">
+        <v>0.9296875</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>731</v>
+      </c>
+      <c r="B732" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>732</v>
+      </c>
+      <c r="B733" t="n">
+        <v>0.95078125</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>733</v>
+      </c>
+      <c r="B734" t="n">
+        <v>0.88890625</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>734</v>
+      </c>
+      <c r="B735" t="n">
+        <v>0.6990625</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>735</v>
+      </c>
+      <c r="B736" t="n">
+        <v>0.2884375</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>736</v>
+      </c>
+      <c r="B737" t="n">
+        <v>0.94796875</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>737</v>
+      </c>
+      <c r="B738" t="n">
+        <v>0.7173437499999999</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>738</v>
+      </c>
+      <c r="B739" t="n">
+        <v>0.9859375</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>739</v>
+      </c>
+      <c r="B740" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>740</v>
+      </c>
+      <c r="B741" t="n">
+        <v>0.8115625</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>741</v>
+      </c>
+      <c r="B742" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>742</v>
+      </c>
+      <c r="B743" t="n">
+        <v>0.97328125</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>743</v>
+      </c>
+      <c r="B744" t="n">
+        <v>0.89171875</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>744</v>
+      </c>
+      <c r="B745" t="n">
+        <v>0.89734375</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>745</v>
+      </c>
+      <c r="B746" t="n">
+        <v>0.5921875</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>746</v>
+      </c>
+      <c r="B747" t="n">
+        <v>0.97046875</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>747</v>
+      </c>
+      <c r="B748" t="n">
+        <v>0.5021875</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>748</v>
+      </c>
+      <c r="B749" t="n">
+        <v>0.82703125</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>749</v>
+      </c>
+      <c r="B750" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>750</v>
+      </c>
+      <c r="B751" t="n">
+        <v>0.9409375</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>751</v>
+      </c>
+      <c r="B752" t="n">
+        <v>0.8509375</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>752</v>
+      </c>
+      <c r="B753" t="n">
+        <v>0.955</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>753</v>
+      </c>
+      <c r="B754" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>754</v>
+      </c>
+      <c r="B755" t="n">
+        <v>0.859375</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>755</v>
+      </c>
+      <c r="B756" t="n">
+        <v>0.285625</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>756</v>
+      </c>
+      <c r="B757" t="n">
+        <v>0.96203125</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>757</v>
+      </c>
+      <c r="B758" t="n">
+        <v>0.9746875</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>758</v>
+      </c>
+      <c r="B759" t="n">
+        <v>0.97328125</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>759</v>
+      </c>
+      <c r="B760" t="n">
+        <v>0.96203125</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>760</v>
+      </c>
+      <c r="B761" t="n">
+        <v>0.9339062499999999</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>761</v>
+      </c>
+      <c r="B762" t="n">
+        <v>0.2884375</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>762</v>
+      </c>
+      <c r="B763" t="n">
+        <v>0.9578125</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>763</v>
+      </c>
+      <c r="B764" t="n">
+        <v>0.701875</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>764</v>
+      </c>
+      <c r="B765" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>765</v>
+      </c>
+      <c r="B766" t="n">
+        <v>0.64140625</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>766</v>
+      </c>
+      <c r="B767" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>767</v>
+      </c>
+      <c r="B768" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>768</v>
+      </c>
+      <c r="B769" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>769</v>
+      </c>
+      <c r="B770" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>770</v>
+      </c>
+      <c r="B771" t="n">
+        <v>0.75109375</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>771</v>
+      </c>
+      <c r="B772" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>772</v>
+      </c>
+      <c r="B773" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>773</v>
+      </c>
+      <c r="B774" t="n">
+        <v>0.95078125</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>774</v>
+      </c>
+      <c r="B775" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>775</v>
+      </c>
+      <c r="B776" t="n">
+        <v>0.97890625</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>776</v>
+      </c>
+      <c r="B777" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>777</v>
+      </c>
+      <c r="B778" t="n">
+        <v>0.9859375</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>778</v>
+      </c>
+      <c r="B779" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>779</v>
+      </c>
+      <c r="B780" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>780</v>
+      </c>
+      <c r="B781" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>781</v>
+      </c>
+      <c r="B782" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>782</v>
+      </c>
+      <c r="B783" t="n">
+        <v>0.84109375</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>783</v>
+      </c>
+      <c r="B784" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>784</v>
+      </c>
+      <c r="B785" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>785</v>
+      </c>
+      <c r="B786" t="n">
+        <v>0.7089062500000001</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>786</v>
+      </c>
+      <c r="B787" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>787</v>
+      </c>
+      <c r="B788" t="n">
+        <v>0.3503124999999999</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>788</v>
+      </c>
+      <c r="B789" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>789</v>
+      </c>
+      <c r="B790" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>790</v>
+      </c>
+      <c r="B791" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>791</v>
+      </c>
+      <c r="B792" t="n">
+        <v>0.1084375</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>792</v>
+      </c>
+      <c r="B793" t="n">
+        <v>0.3278125000000001</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>793</v>
+      </c>
+      <c r="B794" t="n">
+        <v>0.48390625</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>794</v>
+      </c>
+      <c r="B795" t="n">
+        <v>0.7384375</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>795</v>
+      </c>
+      <c r="B796" t="n">
+        <v>0.915625</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>796</v>
+      </c>
+      <c r="B797" t="n">
+        <v>0.48390625</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>797</v>
+      </c>
+      <c r="B798" t="n">
+        <v>0.87203125</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>798</v>
+      </c>
+      <c r="B799" t="n">
+        <v>0.8875</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>799</v>
+      </c>
+      <c r="B800" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>800</v>
+      </c>
+      <c r="B801" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>801</v>
+      </c>
+      <c r="B802" t="n">
+        <v>0.5696874999999999</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>802</v>
+      </c>
+      <c r="B803" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>803</v>
+      </c>
+      <c r="B804" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>804</v>
+      </c>
+      <c r="B805" t="n">
+        <v>0.3095312499999999</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>805</v>
+      </c>
+      <c r="B806" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>806</v>
+      </c>
+      <c r="B807" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>807</v>
+      </c>
+      <c r="B808" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>808</v>
+      </c>
+      <c r="B809" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>809</v>
+      </c>
+      <c r="B810" t="n">
+        <v>0.61328125</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>810</v>
+      </c>
+      <c r="B811" t="n">
+        <v>0.4149999999999999</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>811</v>
+      </c>
+      <c r="B812" t="n">
+        <v>0.499375</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>812</v>
+      </c>
+      <c r="B813" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>813</v>
+      </c>
+      <c r="B814" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>814</v>
+      </c>
+      <c r="B815" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>815</v>
+      </c>
+      <c r="B816" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>816</v>
+      </c>
+      <c r="B817" t="n">
+        <v>0.8059375</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>817</v>
+      </c>
+      <c r="B818" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>818</v>
+      </c>
+      <c r="B819" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>819</v>
+      </c>
+      <c r="B820" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>820</v>
+      </c>
+      <c r="B821" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>821</v>
+      </c>
+      <c r="B822" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>822</v>
+      </c>
+      <c r="B823" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>823</v>
+      </c>
+      <c r="B824" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>824</v>
+      </c>
+      <c r="B825" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>825</v>
+      </c>
+      <c r="B826" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>826</v>
+      </c>
+      <c r="B827" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>827</v>
+      </c>
+      <c r="B828" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>828</v>
+      </c>
+      <c r="B829" t="n">
+        <v>0.48953125</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>829</v>
+      </c>
+      <c r="B830" t="n">
+        <v>0.6090625000000001</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>830</v>
+      </c>
+      <c r="B831" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>831</v>
+      </c>
+      <c r="B832" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>832</v>
+      </c>
+      <c r="B833" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>833</v>
+      </c>
+      <c r="B834" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>834</v>
+      </c>
+      <c r="B835" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>835</v>
+      </c>
+      <c r="B836" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>836</v>
+      </c>
+      <c r="B837" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>837</v>
+      </c>
+      <c r="B838" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>838</v>
+      </c>
+      <c r="B839" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>839</v>
+      </c>
+      <c r="B840" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>840</v>
+      </c>
+      <c r="B841" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>841</v>
+      </c>
+      <c r="B842" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>842</v>
+      </c>
+      <c r="B843" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>843</v>
+      </c>
+      <c r="B844" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>844</v>
+      </c>
+      <c r="B845" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>845</v>
+      </c>
+      <c r="B846" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>846</v>
+      </c>
+      <c r="B847" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>847</v>
+      </c>
+      <c r="B848" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>848</v>
+      </c>
+      <c r="B849" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>849</v>
+      </c>
+      <c r="B850" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>850</v>
+      </c>
+      <c r="B851" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>851</v>
+      </c>
+      <c r="B852" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>852</v>
+      </c>
+      <c r="B853" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>853</v>
+      </c>
+      <c r="B854" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>854</v>
+      </c>
+      <c r="B855" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>855</v>
+      </c>
+      <c r="B856" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>856</v>
+      </c>
+      <c r="B857" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>857</v>
+      </c>
+      <c r="B858" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>858</v>
+      </c>
+      <c r="B859" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>859</v>
+      </c>
+      <c r="B860" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>860</v>
+      </c>
+      <c r="B861" t="n">
+        <v>0.4459375</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>861</v>
+      </c>
+      <c r="B862" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>862</v>
+      </c>
+      <c r="B863" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>863</v>
+      </c>
+      <c r="B864" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>864</v>
+      </c>
+      <c r="B865" t="n">
+        <v>0.521875</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>865</v>
+      </c>
+      <c r="B866" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>866</v>
+      </c>
+      <c r="B867" t="n">
+        <v>0.2954687499999999</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>867</v>
+      </c>
+      <c r="B868" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>868</v>
+      </c>
+      <c r="B869" t="n">
+        <v>0.48671875</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>869</v>
+      </c>
+      <c r="B870" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>870</v>
+      </c>
+      <c r="B871" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>871</v>
+      </c>
+      <c r="B872" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>872</v>
+      </c>
+      <c r="B873" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>873</v>
+      </c>
+      <c r="B874" t="n">
+        <v>0.6034375000000001</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>874</v>
+      </c>
+      <c r="B875" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>875</v>
+      </c>
+      <c r="B876" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>876</v>
+      </c>
+      <c r="B877" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>877</v>
+      </c>
+      <c r="B878" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>878</v>
+      </c>
+      <c r="B879" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>879</v>
+      </c>
+      <c r="B880" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>880</v>
+      </c>
+      <c r="B881" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="n">
+        <v>881</v>
+      </c>
+      <c r="B882" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="n">
+        <v>882</v>
+      </c>
+      <c r="B883" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="n">
+        <v>883</v>
+      </c>
+      <c r="B884" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="n">
+        <v>884</v>
+      </c>
+      <c r="B885" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="n">
+        <v>885</v>
+      </c>
+      <c r="B886" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="n">
+        <v>886</v>
+      </c>
+      <c r="B887" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="n">
+        <v>887</v>
+      </c>
+      <c r="B888" t="n">
+        <v>0.308125</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="n">
+        <v>888</v>
+      </c>
+      <c r="B889" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="n">
+        <v>889</v>
+      </c>
+      <c r="B890" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="n">
+        <v>890</v>
+      </c>
+      <c r="B891" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="n">
+        <v>891</v>
+      </c>
+      <c r="B892" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>892</v>
+      </c>
+      <c r="B893" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>893</v>
+      </c>
+      <c r="B894" t="n">
+        <v>0.6484375</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="n">
+        <v>894</v>
+      </c>
+      <c r="B895" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="n">
+        <v>895</v>
+      </c>
+      <c r="B896" t="n">
+        <v>0.8579687499999999</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="n">
+        <v>896</v>
+      </c>
+      <c r="B897" t="n">
+        <v>0.62171875</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="n">
+        <v>897</v>
+      </c>
+      <c r="B898" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="n">
+        <v>898</v>
+      </c>
+      <c r="B899" t="n">
+        <v>0.713125</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="n">
+        <v>899</v>
+      </c>
+      <c r="B900" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="n">
+        <v>900</v>
+      </c>
+      <c r="B901" t="n">
+        <v>0.859375</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n">
+        <v>901</v>
+      </c>
+      <c r="B902" t="n">
+        <v>0.84671875</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="n">
+        <v>902</v>
+      </c>
+      <c r="B903" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="n">
+        <v>903</v>
+      </c>
+      <c r="B904" t="n">
+        <v>0.4360937499999999</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>904</v>
+      </c>
+      <c r="B905" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="n">
+        <v>905</v>
+      </c>
+      <c r="B906" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="n">
+        <v>906</v>
+      </c>
+      <c r="B907" t="n">
+        <v>0.2715625</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="n">
+        <v>907</v>
+      </c>
+      <c r="B908" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="n">
+        <v>908</v>
+      </c>
+      <c r="B909" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="n">
+        <v>909</v>
+      </c>
+      <c r="B910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n">
+        <v>910</v>
+      </c>
+      <c r="B911" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="n">
+        <v>911</v>
+      </c>
+      <c r="B912" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>912</v>
+      </c>
+      <c r="B913" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>913</v>
+      </c>
+      <c r="B914" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>914</v>
+      </c>
+      <c r="B915" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>915</v>
+      </c>
+      <c r="B916" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="n">
+        <v>916</v>
+      </c>
+      <c r="B917" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>917</v>
+      </c>
+      <c r="B918" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>918</v>
+      </c>
+      <c r="B919" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>919</v>
+      </c>
+      <c r="B920" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="n">
+        <v>920</v>
+      </c>
+      <c r="B921" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="n">
+        <v>921</v>
+      </c>
+      <c r="B922" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="n">
+        <v>922</v>
+      </c>
+      <c r="B923" t="n">
+        <v>0.3714062499999999</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="n">
+        <v>923</v>
+      </c>
+      <c r="B924" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="n">
+        <v>924</v>
+      </c>
+      <c r="B925" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="n">
+        <v>925</v>
+      </c>
+      <c r="B926" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="n">
+        <v>926</v>
+      </c>
+      <c r="B927" t="n">
+        <v>0.73421875</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="n">
+        <v>927</v>
+      </c>
+      <c r="B928" t="n">
+        <v>0.58375</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="n">
+        <v>928</v>
+      </c>
+      <c r="B929" t="n">
+        <v>0.2307812499999999</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="n">
+        <v>929</v>
+      </c>
+      <c r="B930" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="n">
+        <v>930</v>
+      </c>
+      <c r="B931" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="n">
+        <v>931</v>
+      </c>
+      <c r="B932" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="n">
+        <v>932</v>
+      </c>
+      <c r="B933" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="n">
+        <v>933</v>
+      </c>
+      <c r="B934" t="n">
+        <v>0.7159375</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="n">
+        <v>934</v>
+      </c>
+      <c r="B935" t="n">
+        <v>0.81578125</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="n">
+        <v>935</v>
+      </c>
+      <c r="B936" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="n">
+        <v>936</v>
+      </c>
+      <c r="B937" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="n">
+        <v>937</v>
+      </c>
+      <c r="B938" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="n">
+        <v>938</v>
+      </c>
+      <c r="B939" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="n">
+        <v>939</v>
+      </c>
+      <c r="B940" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="n">
+        <v>940</v>
+      </c>
+      <c r="B941" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="n">
+        <v>941</v>
+      </c>
+      <c r="B942" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="n">
+        <v>942</v>
+      </c>
+      <c r="B943" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>943</v>
+      </c>
+      <c r="B944" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>944</v>
+      </c>
+      <c r="B945" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>945</v>
+      </c>
+      <c r="B946" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>946</v>
+      </c>
+      <c r="B947" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>947</v>
+      </c>
+      <c r="B948" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>948</v>
+      </c>
+      <c r="B949" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>949</v>
+      </c>
+      <c r="B950" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>950</v>
+      </c>
+      <c r="B951" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>951</v>
+      </c>
+      <c r="B952" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>952</v>
+      </c>
+      <c r="B953" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>953</v>
+      </c>
+      <c r="B954" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>954</v>
+      </c>
+      <c r="B955" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>955</v>
+      </c>
+      <c r="B956" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>956</v>
+      </c>
+      <c r="B957" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>957</v>
+      </c>
+      <c r="B958" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>958</v>
+      </c>
+      <c r="B959" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>959</v>
+      </c>
+      <c r="B960" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>960</v>
+      </c>
+      <c r="B961" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="n">
+        <v>961</v>
+      </c>
+      <c r="B962" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="n">
+        <v>962</v>
+      </c>
+      <c r="B963" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="n">
+        <v>963</v>
+      </c>
+      <c r="B964" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="n">
+        <v>964</v>
+      </c>
+      <c r="B965" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="n">
+        <v>965</v>
+      </c>
+      <c r="B966" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="n">
+        <v>966</v>
+      </c>
+      <c r="B967" t="n">
+        <v>0.5078125</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="n">
+        <v>967</v>
+      </c>
+      <c r="B968" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="n">
+        <v>968</v>
+      </c>
+      <c r="B969" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="n">
+        <v>969</v>
+      </c>
+      <c r="B970" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="n">
+        <v>970</v>
+      </c>
+      <c r="B971" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="n">
+        <v>971</v>
+      </c>
+      <c r="B972" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="n">
+        <v>972</v>
+      </c>
+      <c r="B973" t="n">
+        <v>0.1590625</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="n">
+        <v>973</v>
+      </c>
+      <c r="B974" t="n">
+        <v>0.25046875</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="n">
+        <v>974</v>
+      </c>
+      <c r="B975" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="n">
+        <v>975</v>
+      </c>
+      <c r="B976" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="n">
+        <v>976</v>
+      </c>
+      <c r="B977" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>977</v>
+      </c>
+      <c r="B978" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>978</v>
+      </c>
+      <c r="B979" t="n">
+        <v>0.1520312500000001</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>979</v>
+      </c>
+      <c r="B980" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>980</v>
+      </c>
+      <c r="B981" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>981</v>
+      </c>
+      <c r="B982" t="n">
+        <v>0.6695312499999999</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>982</v>
+      </c>
+      <c r="B983" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>983</v>
+      </c>
+      <c r="B984" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>984</v>
+      </c>
+      <c r="B985" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>985</v>
+      </c>
+      <c r="B986" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>986</v>
+      </c>
+      <c r="B987" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>987</v>
+      </c>
+      <c r="B988" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>988</v>
+      </c>
+      <c r="B989" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="n">
+        <v>989</v>
+      </c>
+      <c r="B990" t="n">
+        <v>0.521875</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="n">
+        <v>990</v>
+      </c>
+      <c r="B991" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n">
+        <v>991</v>
+      </c>
+      <c r="B992" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="n">
+        <v>992</v>
+      </c>
+      <c r="B993" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="n">
+        <v>993</v>
+      </c>
+      <c r="B994" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="n">
+        <v>994</v>
+      </c>
+      <c r="B995" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="n">
+        <v>995</v>
+      </c>
+      <c r="B996" t="n">
+        <v>0.60203125</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="n">
+        <v>996</v>
+      </c>
+      <c r="B997" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="n">
+        <v>997</v>
+      </c>
+      <c r="B998" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="n">
+        <v>998</v>
+      </c>
+      <c r="B999" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="n">
+        <v>999</v>
+      </c>
+      <c r="B1000" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B1001" t="n">
         <v>0</v>
       </c>
     </row>

--- a/door_switch_maze/grid/DISRC_nor/episode_rewards_disrc.xlsx
+++ b/door_switch_maze/grid/DISRC_nor/episode_rewards_disrc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1001"/>
+  <dimension ref="A1:B701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,7 +709,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>0.4417187499999999</v>
       </c>
     </row>
     <row r="36">
@@ -805,7 +805,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.5992187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -829,7 +829,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.49515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -869,7 +869,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -877,7 +877,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1534374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1013,7 +1013,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>0.28421875</v>
       </c>
     </row>
     <row r="74">
@@ -1157,7 +1157,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>0.20125</v>
       </c>
     </row>
     <row r="92">
@@ -1221,7 +1221,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>0.28984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -1309,7 +1309,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>0.20546875</v>
       </c>
     </row>
     <row r="111">
@@ -1317,7 +1317,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>0.2392187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1389,7 +1389,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -1405,7 +1405,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>0.5879687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1453,7 +1453,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>0.13234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -1461,7 +1461,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>0.5978125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -1477,7 +1477,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>0.3742187499999999</v>
       </c>
     </row>
     <row r="132">
@@ -1485,7 +1485,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>0.17875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -1493,7 +1493,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>0.5992187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -1501,7 +1501,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>0.1520312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -1533,7 +1533,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>0.49515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -1541,7 +1541,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>0.9015625</v>
+        <v>0.578125</v>
       </c>
     </row>
     <row r="140">
@@ -1557,7 +1557,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>0.8284374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -1573,7 +1573,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>0.5795312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -1581,7 +1581,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>0.18578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -1589,7 +1589,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>0.78625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -1597,7 +1597,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>0.4360937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -1605,7 +1605,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>0.81578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -1613,7 +1613,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>0.3671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -1621,7 +1621,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>0.7975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -1629,7 +1629,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>0.4093749999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -1637,7 +1637,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>0.34046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -1645,7 +1645,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>0.1576562500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -1653,7 +1653,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>0.1365625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -1677,7 +1677,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>0.42203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -1701,7 +1701,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>0.34609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -1725,7 +1725,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>0.32640625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -1733,7 +1733,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -1741,7 +1741,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>0.6399999999999999</v>
       </c>
     </row>
     <row r="165">
@@ -1765,7 +1765,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>0.81296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -1773,7 +1773,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>0.3390624999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -1781,7 +1781,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>0.41078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -1789,7 +1789,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>0.31234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -1821,7 +1821,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>0.6737500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -1885,7 +1885,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>0.4360937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -1933,7 +1933,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>0.2546875</v>
       </c>
     </row>
     <row r="189">
@@ -1941,7 +1941,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>0.341875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -1965,7 +1965,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>0.1182812499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -2005,7 +2005,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>0.4178125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -2013,7 +2013,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>0.1084375</v>
+        <v>0.7496875000000001</v>
       </c>
     </row>
     <row r="199">
@@ -2045,7 +2045,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>0</v>
+        <v>0.5035937500000001</v>
       </c>
     </row>
     <row r="203">
@@ -2053,7 +2053,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>0.45296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -2077,7 +2077,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>0.724375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -2085,7 +2085,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>0.6371875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -2093,7 +2093,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>0.926875</v>
+        <v>0.35734375</v>
       </c>
     </row>
     <row r="209">
@@ -2101,7 +2101,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>0.95359375</v>
+        <v>0.3039062499999999</v>
       </c>
     </row>
     <row r="210">
@@ -2117,7 +2117,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>0.6385937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -2125,7 +2125,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>0.488125</v>
+        <v>0.2982812500000001</v>
       </c>
     </row>
     <row r="213">
@@ -2133,7 +2133,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>0.803125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -2141,7 +2141,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>0.5246875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -2157,7 +2157,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>0.7946875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -2165,7 +2165,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>0.4009374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -2181,7 +2181,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>0.8875</v>
+        <v>0.20828125</v>
       </c>
     </row>
     <row r="220">
@@ -2189,7 +2189,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>0.5992187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -2197,7 +2197,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>0.7975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -2205,7 +2205,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>0.34046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -2237,7 +2237,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>0.47265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -2245,7 +2245,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>0.780625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -2253,7 +2253,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>0.8396875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -2261,7 +2261,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>0.5767187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -2269,7 +2269,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>0.91984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -2277,7 +2277,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>0.8509375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -2285,7 +2285,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>0.8509375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -2293,7 +2293,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>0.938125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -2301,7 +2301,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>0.94796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -2309,7 +2309,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>0.5303125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -2317,7 +2317,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>0.6596875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -2325,7 +2325,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>0.80734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -2341,7 +2341,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>0.5457812500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -2349,7 +2349,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>0.6737500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -2357,7 +2357,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>0.8987499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -2365,7 +2365,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>0.90578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -2389,7 +2389,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>0.8875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -2397,7 +2397,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>0.94234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -2405,7 +2405,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>0.88328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -2413,7 +2413,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>0.84109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -2421,7 +2421,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>0.8495312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -2429,7 +2429,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>0.62171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -2453,7 +2453,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>0.7229687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -2461,7 +2461,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>0.91984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -2469,7 +2469,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>0.39671875</v>
       </c>
     </row>
     <row r="256">
@@ -2477,7 +2477,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>0.8143750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -2485,7 +2485,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>0.89453125</v>
+        <v>0.5401562499999999</v>
       </c>
     </row>
     <row r="258">
@@ -2493,7 +2493,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>0</v>
+        <v>0.8509375</v>
       </c>
     </row>
     <row r="259">
@@ -2509,7 +2509,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>0.91</v>
+        <v>0.40796875</v>
       </c>
     </row>
     <row r="261">
@@ -2517,7 +2517,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>0.88890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -2525,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>0.60765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -2533,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="n">
-        <v>0.68640625</v>
+        <v>0.73703125</v>
       </c>
     </row>
     <row r="264">
@@ -2557,7 +2557,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>0.9409375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -2565,7 +2565,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>0.96484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -2581,7 +2581,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>0.9071875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -2589,7 +2589,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>0.7454687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -2597,7 +2597,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>0.9015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -2605,7 +2605,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="n">
-        <v>0</v>
+        <v>0.3615625</v>
       </c>
     </row>
     <row r="273">
@@ -2613,7 +2613,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>0.9128125</v>
+        <v>0.7215625</v>
       </c>
     </row>
     <row r="274">
@@ -2621,7 +2621,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="n">
-        <v>0.89171875</v>
+        <v>0.5823437499999999</v>
       </c>
     </row>
     <row r="275">
@@ -2645,7 +2645,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>0.803125</v>
+        <v>0.4628125</v>
       </c>
     </row>
     <row r="278">
@@ -2653,7 +2653,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>0.308125</v>
       </c>
     </row>
     <row r="279">
@@ -2661,7 +2661,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="n">
-        <v>0.7229687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -2677,7 +2677,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>0.8607812500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -2685,7 +2685,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>0.55140625</v>
+        <v>0.8256250000000001</v>
       </c>
     </row>
     <row r="283">
@@ -2693,7 +2693,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>0</v>
+        <v>0.8340624999999999</v>
       </c>
     </row>
     <row r="284">
@@ -2701,7 +2701,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>0.9015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -2709,7 +2709,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="n">
-        <v>0.93671875</v>
+        <v>0.1646875</v>
       </c>
     </row>
     <row r="286">
@@ -2717,7 +2717,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>0.2828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -2725,7 +2725,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>0.701875</v>
+        <v>0.1675</v>
       </c>
     </row>
     <row r="288">
@@ -2741,7 +2741,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>0.971875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -2749,7 +2749,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>0.16609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -2757,7 +2757,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>0.87765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -2773,7 +2773,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="n">
-        <v>0.9662500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -2789,7 +2789,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>0.3784375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -2805,7 +2805,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="n">
-        <v>0.3109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -2813,7 +2813,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0.6203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -2821,7 +2821,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>0.9325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -2829,7 +2829,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>0.5992187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -2837,7 +2837,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>0.8495312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -2845,7 +2845,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>0.8692187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -2853,7 +2853,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="n">
-        <v>0.9521875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -2861,7 +2861,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>0.775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -2877,7 +2877,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="n">
-        <v>0.7285937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -2885,7 +2885,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="n">
-        <v>0.36015625</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="308">
@@ -2893,7 +2893,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>0</v>
+        <v>0.85375</v>
       </c>
     </row>
     <row r="309">
@@ -2901,7 +2901,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>0.6934374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -2909,7 +2909,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>0.701875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -2917,7 +2917,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="n">
-        <v>0.5879687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -2941,7 +2941,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>0.926875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -2949,7 +2949,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>0.74265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -2957,7 +2957,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="n">
-        <v>0.8256250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -2965,7 +2965,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>0.76515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -2973,7 +2973,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="n">
-        <v>0.4698437499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -2981,7 +2981,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="n">
-        <v>0.8987499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -2989,7 +2989,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>0.91140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -3005,7 +3005,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>0.836875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -3013,7 +3013,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="n">
-        <v>0.2153125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -3029,7 +3029,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>0.38828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -3037,7 +3037,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="n">
-        <v>0.9071875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -3053,7 +3053,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -3061,7 +3061,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
-        <v>0.7609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -3069,7 +3069,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>0.9465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -3085,7 +3085,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="n">
-        <v>0</v>
+        <v>0.218125</v>
       </c>
     </row>
     <row r="333">
@@ -3093,7 +3093,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="n">
-        <v>0.870625</v>
+        <v>0.32640625</v>
       </c>
     </row>
     <row r="334">
@@ -3101,7 +3101,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="n">
-        <v>0.96765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -3109,7 +3109,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="n">
-        <v>0</v>
+        <v>0.1899999999999999</v>
       </c>
     </row>
     <row r="336">
@@ -3117,7 +3117,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="n">
-        <v>0</v>
+        <v>0.2940624999999999</v>
       </c>
     </row>
     <row r="337">
@@ -3125,7 +3125,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="n">
-        <v>0.949375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -3133,7 +3133,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="n">
-        <v>0.81015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -3141,7 +3141,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="n">
-        <v>0.8425</v>
+        <v>0.5049999999999999</v>
       </c>
     </row>
     <row r="340">
@@ -3149,7 +3149,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>0.7876562499999999</v>
+        <v>0.713125</v>
       </c>
     </row>
     <row r="341">
@@ -3157,7 +3157,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="n">
-        <v>0.8734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -3165,7 +3165,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>0.3629687500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -3181,7 +3181,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="n">
-        <v>0.8959375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -3197,7 +3197,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="n">
-        <v>0.80453125</v>
+        <v>0.465625</v>
       </c>
     </row>
     <row r="347">
@@ -3205,7 +3205,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>0.91703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -3213,7 +3213,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="n">
-        <v>0.6653125</v>
+        <v>0.68078125</v>
       </c>
     </row>
     <row r="349">
@@ -3221,7 +3221,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="n">
-        <v>0.7229687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -3229,7 +3229,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="n">
-        <v>0.4332812500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -3237,7 +3237,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="n">
-        <v>0.9634374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -3253,7 +3253,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="n">
-        <v>0</v>
+        <v>0.81296875</v>
       </c>
     </row>
     <row r="354">
@@ -3261,7 +3261,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -3269,7 +3269,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="n">
-        <v>0.7173437499999999</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="356">
@@ -3277,7 +3277,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="n">
-        <v>0.746875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -3293,7 +3293,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -3301,7 +3301,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="n">
-        <v>0.7496875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -3309,7 +3309,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="n">
-        <v>0.9240625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -3317,7 +3317,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="n">
-        <v>0.780625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -3325,7 +3325,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>0.8509375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -3333,7 +3333,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="n">
-        <v>0.78625</v>
+        <v>0.2335937499999999</v>
       </c>
     </row>
     <row r="364">
@@ -3341,7 +3341,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="n">
-        <v>0.848125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -3349,7 +3349,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="n">
-        <v>0.4965625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -3357,7 +3357,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="n">
-        <v>0.2771875</v>
+        <v>0.6118749999999999</v>
       </c>
     </row>
     <row r="367">
@@ -3365,7 +3365,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="n">
-        <v>0.6751562499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -3373,7 +3373,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="n">
-        <v>0.983125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
@@ -3389,7 +3389,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="n">
-        <v>0.62171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -3397,7 +3397,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>0.95640625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -3405,7 +3405,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>0.904375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -3413,7 +3413,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="n">
-        <v>0.8143750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -3421,7 +3421,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="n">
-        <v>0.9662500000000001</v>
+        <v>0.12109375</v>
       </c>
     </row>
     <row r="375">
@@ -3429,7 +3429,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="n">
-        <v>0</v>
+        <v>0.4740625000000001</v>
       </c>
     </row>
     <row r="376">
@@ -3437,7 +3437,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="n">
-        <v>0.3446874999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -3445,7 +3445,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>0</v>
+        <v>0.8565625</v>
       </c>
     </row>
     <row r="378">
@@ -3461,7 +3461,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="n">
-        <v>0.88609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -3477,7 +3477,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>0.9353125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -3493,7 +3493,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="n">
-        <v>0.92265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -3501,7 +3501,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>0.9690625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -3509,7 +3509,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="n">
-        <v>0.9578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -3517,7 +3517,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>0</v>
+        <v>0.5246875</v>
       </c>
     </row>
     <row r="387">
@@ -3533,7 +3533,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>0</v>
+        <v>0.62171875</v>
       </c>
     </row>
     <row r="389">
@@ -3541,7 +3541,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>0.5823437499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -3565,7 +3565,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="n">
-        <v>0.92125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -3573,7 +3573,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="n">
-        <v>0.668125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -3581,7 +3581,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="n">
-        <v>0.97609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -3597,7 +3597,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>0.85515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -3613,7 +3613,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>0.9310937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -3621,7 +3621,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="n">
-        <v>0.8171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -3629,7 +3629,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="n">
-        <v>0.88890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -3637,7 +3637,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="n">
-        <v>0.83265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -3645,7 +3645,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -3653,7 +3653,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="n">
-        <v>0.8579687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -3669,7 +3669,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="n">
-        <v>0.6498437500000001</v>
+        <v>0.6442187500000001</v>
       </c>
     </row>
     <row r="406">
@@ -3677,7 +3677,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="n">
-        <v>0.87625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -3693,7 +3693,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="n">
-        <v>0</v>
+        <v>0.6695312499999999</v>
       </c>
     </row>
     <row r="409">
@@ -3701,7 +3701,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="n">
-        <v>0.91703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -3709,7 +3709,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="n">
-        <v>0.9310937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -3717,7 +3717,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.161875</v>
       </c>
     </row>
     <row r="412">
@@ -3725,7 +3725,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="n">
-        <v>0.48390625</v>
+        <v>0.20125</v>
       </c>
     </row>
     <row r="413">
@@ -3733,7 +3733,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="n">
-        <v>0.75671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -3741,7 +3741,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="n">
-        <v>0.55140625</v>
+        <v>0.13515625</v>
       </c>
     </row>
     <row r="415">
@@ -3749,7 +3749,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="n">
-        <v>0.848125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416">
@@ -3757,7 +3757,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="n">
-        <v>0.18296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -3765,7 +3765,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="n">
-        <v>0.71171875</v>
+        <v>0.938125</v>
       </c>
     </row>
     <row r="418">
@@ -3781,7 +3781,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="n">
-        <v>0.89453125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -3789,7 +3789,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421">
@@ -3797,7 +3797,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="n">
-        <v>0.9690625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="422">
@@ -3805,7 +3805,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="n">
-        <v>0.48390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -3821,7 +3821,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="n">
-        <v>0.40234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425">
@@ -3829,7 +3829,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="n">
-        <v>0.83828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -3845,7 +3845,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="n">
-        <v>0.7524999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -3853,7 +3853,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="n">
-        <v>0.89734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429">
@@ -3861,7 +3861,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="n">
-        <v>0</v>
+        <v>0.6259375</v>
       </c>
     </row>
     <row r="430">
@@ -3869,7 +3869,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="n">
-        <v>0</v>
+        <v>0.66109375</v>
       </c>
     </row>
     <row r="431">
@@ -3877,7 +3877,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="n">
-        <v>0.32640625</v>
+        <v>0.7946875</v>
       </c>
     </row>
     <row r="432">
@@ -3885,7 +3885,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="n">
-        <v>0.81859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -3909,7 +3909,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="n">
-        <v>0.595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -3917,7 +3917,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="n">
-        <v>0.91421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -3925,7 +3925,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="n">
-        <v>0.81859375</v>
+        <v>0.60625</v>
       </c>
     </row>
     <row r="438">
@@ -3933,7 +3933,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>0.34890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -3941,7 +3941,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>0.95078125</v>
+        <v>0.555625</v>
       </c>
     </row>
     <row r="440">
@@ -3973,7 +3973,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="n">
-        <v>0</v>
+        <v>0.75671875</v>
       </c>
     </row>
     <row r="444">
@@ -3981,7 +3981,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="n">
-        <v>0.91</v>
+        <v>0.589375</v>
       </c>
     </row>
     <row r="445">
@@ -3989,7 +3989,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="n">
-        <v>0.94515625</v>
+        <v>0.5078125</v>
       </c>
     </row>
     <row r="446">
@@ -3997,7 +3997,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="n">
-        <v>0.4796874999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
@@ -4013,7 +4013,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="n">
-        <v>0.465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449">
@@ -4021,7 +4021,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="n">
-        <v>0.960625</v>
+        <v>0.61328125</v>
       </c>
     </row>
     <row r="450">
@@ -4029,7 +4029,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="n">
-        <v>0.7271875</v>
+        <v>0.6118749999999999</v>
       </c>
     </row>
     <row r="451">
@@ -4037,7 +4037,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="n">
-        <v>0.91984375</v>
+        <v>0.5767187499999999</v>
       </c>
     </row>
     <row r="452">
@@ -4045,7 +4045,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="n">
-        <v>0.83546875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -4053,7 +4053,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="n">
-        <v>0.724375</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="454">
@@ -4061,7 +4061,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="n">
-        <v>0.9339062499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -4069,7 +4069,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>0.51625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -4077,7 +4077,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="n">
-        <v>0.91421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="457">
@@ -4085,7 +4085,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="n">
-        <v>0.89171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -4093,7 +4093,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="n">
-        <v>0.94515625</v>
+        <v>0.30671875</v>
       </c>
     </row>
     <row r="459">
@@ -4101,7 +4101,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="n">
-        <v>0.84109375</v>
+        <v>0.41078125</v>
       </c>
     </row>
     <row r="460">
@@ -4117,7 +4117,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="n">
-        <v>0</v>
+        <v>0.668125</v>
       </c>
     </row>
     <row r="462">
@@ -4125,7 +4125,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="n">
-        <v>0.8846875</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="463">
@@ -4133,7 +4133,7 @@
         <v>462</v>
       </c>
       <c r="B463" t="n">
-        <v>0.5528124999999999</v>
+        <v>0.5640624999999999</v>
       </c>
     </row>
     <row r="464">
@@ -4141,7 +4141,7 @@
         <v>463</v>
       </c>
       <c r="B464" t="n">
-        <v>0</v>
+        <v>0.61890625</v>
       </c>
     </row>
     <row r="465">
@@ -4149,7 +4149,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="n">
-        <v>0.5640624999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466">
@@ -4157,7 +4157,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="n">
-        <v>0.83828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">
@@ -4165,7 +4165,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="n">
-        <v>0.9465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="468">
@@ -4173,7 +4173,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="n">
-        <v>0.94796875</v>
+        <v>0.5865625</v>
       </c>
     </row>
     <row r="469">
@@ -4181,7 +4181,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="n">
-        <v>0.5640624999999999</v>
+        <v>0.4234375</v>
       </c>
     </row>
     <row r="470">
@@ -4197,7 +4197,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="n">
-        <v>0.881875</v>
+        <v>0.85234375</v>
       </c>
     </row>
     <row r="472">
@@ -4205,7 +4205,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="n">
-        <v>0.85375</v>
+        <v>0.65125</v>
       </c>
     </row>
     <row r="473">
@@ -4213,7 +4213,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="n">
-        <v>0.9310937500000001</v>
+        <v>0.26734375</v>
       </c>
     </row>
     <row r="474">
@@ -4221,7 +4221,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="n">
-        <v>0.97328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -4229,7 +4229,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="n">
-        <v>0.9409375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476">
@@ -4237,7 +4237,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="n">
-        <v>0</v>
+        <v>0.7440625000000001</v>
       </c>
     </row>
     <row r="477">
@@ -4245,7 +4245,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="n">
-        <v>0.7665625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478">
@@ -4261,7 +4261,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="n">
-        <v>0.9803125</v>
+        <v>0.78625</v>
       </c>
     </row>
     <row r="480">
@@ -4269,7 +4269,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="n">
-        <v>0.938125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -4277,7 +4277,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="n">
-        <v>0.84671875</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="482">
@@ -4301,7 +4301,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="n">
-        <v>0</v>
+        <v>0.48953125</v>
       </c>
     </row>
     <row r="485">
@@ -4309,7 +4309,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.769375</v>
       </c>
     </row>
     <row r="486">
@@ -4317,7 +4317,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="n">
-        <v>0.93953125</v>
+        <v>0.80875</v>
       </c>
     </row>
     <row r="487">
@@ -4325,7 +4325,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="n">
-        <v>0.84671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -4341,7 +4341,7 @@
         <v>488</v>
       </c>
       <c r="B489" t="n">
-        <v>0</v>
+        <v>0.81578125</v>
       </c>
     </row>
     <row r="490">
@@ -4349,7 +4349,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="n">
-        <v>0.2040624999999999</v>
+        <v>0.33484375</v>
       </c>
     </row>
     <row r="491">
@@ -4357,7 +4357,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="n">
-        <v>0</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="492">
@@ -4365,7 +4365,7 @@
         <v>491</v>
       </c>
       <c r="B492" t="n">
-        <v>0.90859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493">
@@ -4373,7 +4373,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="n">
-        <v>0.54859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494">
@@ -4389,7 +4389,7 @@
         <v>494</v>
       </c>
       <c r="B495" t="n">
-        <v>0</v>
+        <v>0.3334375000000001</v>
       </c>
     </row>
     <row r="496">
@@ -4405,7 +4405,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="n">
-        <v>0</v>
+        <v>0.56546875</v>
       </c>
     </row>
     <row r="498">
@@ -4421,7 +4421,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="n">
-        <v>0.7089062500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -4429,7 +4429,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="n">
-        <v>0.8959375000000001</v>
+        <v>0.81296875</v>
       </c>
     </row>
     <row r="501">
@@ -4445,7 +4445,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="n">
-        <v>0.2884375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503">
@@ -4453,7 +4453,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="n">
-        <v>0.4684375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="504">
@@ -4469,7 +4469,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="n">
-        <v>0.6034375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506">
@@ -4501,7 +4501,7 @@
         <v>508</v>
       </c>
       <c r="B509" t="n">
-        <v>0.87765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="510">
@@ -4509,7 +4509,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="n">
-        <v>0.8875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511">
@@ -4541,7 +4541,7 @@
         <v>513</v>
       </c>
       <c r="B514" t="n">
-        <v>0.926875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515">
@@ -4557,7 +4557,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="n">
-        <v>0.955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="517">
@@ -4565,7 +4565,7 @@
         <v>516</v>
       </c>
       <c r="B517" t="n">
-        <v>0.66390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518">
@@ -4573,7 +4573,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="n">
-        <v>0.7089062500000001</v>
+        <v>0.62875</v>
       </c>
     </row>
     <row r="519">
@@ -4581,7 +4581,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="n">
-        <v>0.97328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="520">
@@ -4589,7 +4589,7 @@
         <v>519</v>
       </c>
       <c r="B520" t="n">
-        <v>0</v>
+        <v>0.5739062500000001</v>
       </c>
     </row>
     <row r="521">
@@ -4597,7 +4597,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="n">
-        <v>0.1548437499999999</v>
+        <v>0.7440625000000001</v>
       </c>
     </row>
     <row r="522">
@@ -4605,7 +4605,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="n">
-        <v>0</v>
+        <v>0.7975</v>
       </c>
     </row>
     <row r="523">
@@ -4621,7 +4621,7 @@
         <v>523</v>
       </c>
       <c r="B524" t="n">
-        <v>0.7975</v>
+        <v>0.8495312500000001</v>
       </c>
     </row>
     <row r="525">
@@ -4629,7 +4629,7 @@
         <v>524</v>
       </c>
       <c r="B525" t="n">
-        <v>0.91140625</v>
+        <v>0.7637499999999999</v>
       </c>
     </row>
     <row r="526">
@@ -4637,7 +4637,7 @@
         <v>525</v>
       </c>
       <c r="B526" t="n">
-        <v>0</v>
+        <v>0.13515625</v>
       </c>
     </row>
     <row r="527">
@@ -4645,7 +4645,7 @@
         <v>526</v>
       </c>
       <c r="B527" t="n">
-        <v>0.6118749999999999</v>
+        <v>0.8059375</v>
       </c>
     </row>
     <row r="528">
@@ -4653,7 +4653,7 @@
         <v>527</v>
       </c>
       <c r="B528" t="n">
-        <v>0</v>
+        <v>0.926875</v>
       </c>
     </row>
     <row r="529">
@@ -4661,7 +4661,7 @@
         <v>528</v>
       </c>
       <c r="B529" t="n">
-        <v>0.34890625</v>
+        <v>0.3784375</v>
       </c>
     </row>
     <row r="530">
@@ -4669,7 +4669,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="n">
-        <v>0.70609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -4677,7 +4677,7 @@
         <v>530</v>
       </c>
       <c r="B531" t="n">
-        <v>0</v>
+        <v>0.431875</v>
       </c>
     </row>
     <row r="532">
@@ -4693,7 +4693,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="n">
-        <v>0.83265625</v>
+        <v>0.10984375</v>
       </c>
     </row>
     <row r="534">
@@ -4701,7 +4701,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="n">
-        <v>0.8635937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -4709,7 +4709,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="n">
-        <v>0</v>
+        <v>0.8396875</v>
       </c>
     </row>
     <row r="536">
@@ -4717,7 +4717,7 @@
         <v>535</v>
       </c>
       <c r="B536" t="n">
-        <v>0.915625</v>
+        <v>0.8692187499999999</v>
       </c>
     </row>
     <row r="537">
@@ -4733,7 +4733,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="n">
-        <v>0.7159375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539">
@@ -4741,7 +4741,7 @@
         <v>538</v>
       </c>
       <c r="B539" t="n">
-        <v>0.8959375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
@@ -4749,7 +4749,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="541">
@@ -4757,7 +4757,7 @@
         <v>540</v>
       </c>
       <c r="B541" t="n">
-        <v>0.95921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="542">
@@ -4765,7 +4765,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="n">
-        <v>0.79609375</v>
+        <v>0.5767187499999999</v>
       </c>
     </row>
     <row r="543">
@@ -4773,7 +4773,7 @@
         <v>542</v>
       </c>
       <c r="B543" t="n">
-        <v>0</v>
+        <v>0.3503124999999999</v>
       </c>
     </row>
     <row r="544">
@@ -4781,7 +4781,7 @@
         <v>543</v>
       </c>
       <c r="B544" t="n">
-        <v>0.6118749999999999</v>
+        <v>0.77359375</v>
       </c>
     </row>
     <row r="545">
@@ -4789,7 +4789,7 @@
         <v>544</v>
       </c>
       <c r="B545" t="n">
-        <v>0.82421875</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="546">
@@ -4797,7 +4797,7 @@
         <v>545</v>
       </c>
       <c r="B546" t="n">
-        <v>0.5696874999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547">
@@ -4805,7 +4805,7 @@
         <v>546</v>
       </c>
       <c r="B547" t="n">
-        <v>0.8284374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548">
@@ -4821,7 +4821,7 @@
         <v>548</v>
       </c>
       <c r="B549" t="n">
-        <v>0</v>
+        <v>0.1225000000000001</v>
       </c>
     </row>
     <row r="550">
@@ -4837,7 +4837,7 @@
         <v>550</v>
       </c>
       <c r="B551" t="n">
-        <v>0.5879687499999999</v>
+        <v>0.4037500000000001</v>
       </c>
     </row>
     <row r="552">
@@ -4869,7 +4869,7 @@
         <v>554</v>
       </c>
       <c r="B555" t="n">
-        <v>0</v>
+        <v>0.2828125</v>
       </c>
     </row>
     <row r="556">
@@ -4877,7 +4877,7 @@
         <v>555</v>
       </c>
       <c r="B556" t="n">
-        <v>0.82140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557">
@@ -4885,7 +4885,7 @@
         <v>556</v>
       </c>
       <c r="B557" t="n">
-        <v>0.926875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558">
@@ -4893,7 +4893,7 @@
         <v>557</v>
       </c>
       <c r="B558" t="n">
-        <v>0.8987499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559">
@@ -4909,7 +4909,7 @@
         <v>559</v>
       </c>
       <c r="B560" t="n">
-        <v>0.9282812499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="561">
@@ -4917,7 +4917,7 @@
         <v>560</v>
       </c>
       <c r="B561" t="n">
-        <v>0.690625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="562">
@@ -4925,7 +4925,7 @@
         <v>561</v>
       </c>
       <c r="B562" t="n">
-        <v>0.69625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563">
@@ -4933,7 +4933,7 @@
         <v>562</v>
       </c>
       <c r="B563" t="n">
-        <v>0.78484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="564">
@@ -4941,7 +4941,7 @@
         <v>563</v>
       </c>
       <c r="B564" t="n">
-        <v>0.955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565">
@@ -4957,7 +4957,7 @@
         <v>565</v>
       </c>
       <c r="B566" t="n">
-        <v>0.983125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="567">
@@ -4965,7 +4965,7 @@
         <v>566</v>
       </c>
       <c r="B567" t="n">
-        <v>0.91984375</v>
+        <v>0.14078125</v>
       </c>
     </row>
     <row r="568">
@@ -4973,7 +4973,7 @@
         <v>567</v>
       </c>
       <c r="B568" t="n">
-        <v>0.9775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569">
@@ -4981,7 +4981,7 @@
         <v>568</v>
       </c>
       <c r="B569" t="n">
-        <v>0.7496875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570">
@@ -5013,7 +5013,7 @@
         <v>572</v>
       </c>
       <c r="B573" t="n">
-        <v>0.7778125</v>
+        <v>0.4389062500000001</v>
       </c>
     </row>
     <row r="574">
@@ -5021,7 +5021,7 @@
         <v>573</v>
       </c>
       <c r="B574" t="n">
-        <v>0.803125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="575">
@@ -5029,7 +5029,7 @@
         <v>574</v>
       </c>
       <c r="B575" t="n">
-        <v>0.8790625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="576">
@@ -5037,7 +5037,7 @@
         <v>575</v>
       </c>
       <c r="B576" t="n">
-        <v>0.25328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="577">
@@ -5053,7 +5053,7 @@
         <v>577</v>
       </c>
       <c r="B578" t="n">
-        <v>0.66390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="579">
@@ -5061,7 +5061,7 @@
         <v>578</v>
       </c>
       <c r="B579" t="n">
-        <v>0.955</v>
+        <v>0.17171875</v>
       </c>
     </row>
     <row r="580">
@@ -5085,7 +5085,7 @@
         <v>581</v>
       </c>
       <c r="B582" t="n">
-        <v>0</v>
+        <v>0.431875</v>
       </c>
     </row>
     <row r="583">
@@ -5125,7 +5125,7 @@
         <v>586</v>
       </c>
       <c r="B587" t="n">
-        <v>0.66109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="588">
@@ -5149,7 +5149,7 @@
         <v>589</v>
       </c>
       <c r="B590" t="n">
-        <v>0.1632812499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="591">
@@ -5157,7 +5157,7 @@
         <v>590</v>
       </c>
       <c r="B591" t="n">
-        <v>0.73421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="592">
@@ -5189,7 +5189,7 @@
         <v>594</v>
       </c>
       <c r="B595" t="n">
-        <v>0.713125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="596">
@@ -5197,7 +5197,7 @@
         <v>595</v>
       </c>
       <c r="B596" t="n">
-        <v>0.3953125</v>
+        <v>0.578125</v>
       </c>
     </row>
     <row r="597">
@@ -5205,7 +5205,7 @@
         <v>596</v>
       </c>
       <c r="B597" t="n">
-        <v>0.915625</v>
+        <v>0.8931249999999999</v>
       </c>
     </row>
     <row r="598">
@@ -5229,7 +5229,7 @@
         <v>599</v>
       </c>
       <c r="B600" t="n">
-        <v>0.8692187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="601">
@@ -5245,7 +5245,7 @@
         <v>601</v>
       </c>
       <c r="B602" t="n">
-        <v>0.82984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="603">
@@ -5253,7 +5253,7 @@
         <v>602</v>
       </c>
       <c r="B603" t="n">
-        <v>0.555625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="604">
@@ -5269,7 +5269,7 @@
         <v>604</v>
       </c>
       <c r="B605" t="n">
-        <v>0.7215625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="606">
@@ -5277,7 +5277,7 @@
         <v>605</v>
       </c>
       <c r="B606" t="n">
-        <v>0.656875</v>
+        <v>0.5035937500000001</v>
       </c>
     </row>
     <row r="607">
@@ -5285,7 +5285,7 @@
         <v>606</v>
       </c>
       <c r="B607" t="n">
-        <v>0.9353125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="608">
@@ -5317,7 +5317,7 @@
         <v>610</v>
       </c>
       <c r="B611" t="n">
-        <v>0.89453125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="612">
@@ -5325,7 +5325,7 @@
         <v>611</v>
       </c>
       <c r="B612" t="n">
-        <v>0.95921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="613">
@@ -5333,7 +5333,7 @@
         <v>612</v>
       </c>
       <c r="B613" t="n">
-        <v>0.82703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -5341,7 +5341,7 @@
         <v>613</v>
       </c>
       <c r="B614" t="n">
-        <v>0.78625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
@@ -5349,7 +5349,7 @@
         <v>614</v>
       </c>
       <c r="B615" t="n">
-        <v>0.97609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="616">
@@ -5357,7 +5357,7 @@
         <v>615</v>
       </c>
       <c r="B616" t="n">
-        <v>0.9409375</v>
+        <v>0.73140625</v>
       </c>
     </row>
     <row r="617">
@@ -5365,7 +5365,7 @@
         <v>616</v>
       </c>
       <c r="B617" t="n">
-        <v>0.91703125</v>
+        <v>0.8495312500000001</v>
       </c>
     </row>
     <row r="618">
@@ -5373,7 +5373,7 @@
         <v>617</v>
       </c>
       <c r="B618" t="n">
-        <v>0.9310937500000001</v>
+        <v>0.85515625</v>
       </c>
     </row>
     <row r="619">
@@ -5381,7 +5381,7 @@
         <v>618</v>
       </c>
       <c r="B619" t="n">
-        <v>0.5092187500000001</v>
+        <v>0.4065624999999999</v>
       </c>
     </row>
     <row r="620">
@@ -5405,7 +5405,7 @@
         <v>621</v>
       </c>
       <c r="B622" t="n">
-        <v>0.6695312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
@@ -5413,7 +5413,7 @@
         <v>622</v>
       </c>
       <c r="B623" t="n">
-        <v>0.91703125</v>
+        <v>0.54859375</v>
       </c>
     </row>
     <row r="624">
@@ -5421,7 +5421,7 @@
         <v>623</v>
       </c>
       <c r="B624" t="n">
-        <v>0.7581249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="625">
@@ -5437,7 +5437,7 @@
         <v>625</v>
       </c>
       <c r="B626" t="n">
-        <v>0</v>
+        <v>0.6934374999999999</v>
       </c>
     </row>
     <row r="627">
@@ -5445,7 +5445,7 @@
         <v>626</v>
       </c>
       <c r="B627" t="n">
-        <v>0.735625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="628">
@@ -5453,7 +5453,7 @@
         <v>627</v>
       </c>
       <c r="B628" t="n">
-        <v>0.95921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="629">
@@ -5469,7 +5469,7 @@
         <v>629</v>
       </c>
       <c r="B630" t="n">
-        <v>0.87765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="631">
@@ -5477,7 +5477,7 @@
         <v>630</v>
       </c>
       <c r="B631" t="n">
-        <v>0.95078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="632">
@@ -5485,7 +5485,7 @@
         <v>631</v>
       </c>
       <c r="B632" t="n">
-        <v>0.701875</v>
+        <v>0.7637499999999999</v>
       </c>
     </row>
     <row r="633">
@@ -5501,7 +5501,7 @@
         <v>633</v>
       </c>
       <c r="B634" t="n">
-        <v>0.75390625</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="635">
@@ -5517,7 +5517,7 @@
         <v>635</v>
       </c>
       <c r="B636" t="n">
-        <v>0.95921875</v>
+        <v>0.5190625</v>
       </c>
     </row>
     <row r="637">
@@ -5525,7 +5525,7 @@
         <v>636</v>
       </c>
       <c r="B637" t="n">
-        <v>0.96203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="638">
@@ -5533,7 +5533,7 @@
         <v>637</v>
       </c>
       <c r="B638" t="n">
-        <v>0</v>
+        <v>0.7792187500000001</v>
       </c>
     </row>
     <row r="639">
@@ -5541,7 +5541,7 @@
         <v>638</v>
       </c>
       <c r="B639" t="n">
-        <v>0.92125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640">
@@ -5549,7 +5549,7 @@
         <v>639</v>
       </c>
       <c r="B640" t="n">
-        <v>0.85375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="641">
@@ -5565,7 +5565,7 @@
         <v>641</v>
       </c>
       <c r="B642" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="643">
@@ -5573,7 +5573,7 @@
         <v>642</v>
       </c>
       <c r="B643" t="n">
-        <v>0.9128125</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="644">
@@ -5581,7 +5581,7 @@
         <v>643</v>
       </c>
       <c r="B644" t="n">
-        <v>0.19984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="645">
@@ -5589,7 +5589,7 @@
         <v>644</v>
       </c>
       <c r="B645" t="n">
-        <v>0</v>
+        <v>0.4093749999999999</v>
       </c>
     </row>
     <row r="646">
@@ -5613,7 +5613,7 @@
         <v>647</v>
       </c>
       <c r="B648" t="n">
-        <v>0.9662500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="649">
@@ -5629,7 +5629,7 @@
         <v>649</v>
       </c>
       <c r="B650" t="n">
-        <v>0.93671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="651">
@@ -5645,7 +5645,7 @@
         <v>651</v>
       </c>
       <c r="B652" t="n">
-        <v>0.9128125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="653">
@@ -5653,7 +5653,7 @@
         <v>652</v>
       </c>
       <c r="B653" t="n">
-        <v>0</v>
+        <v>0.8284374999999999</v>
       </c>
     </row>
     <row r="654">
@@ -5661,7 +5661,7 @@
         <v>653</v>
       </c>
       <c r="B654" t="n">
-        <v>0.94515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="655">
@@ -5677,7 +5677,7 @@
         <v>655</v>
       </c>
       <c r="B656" t="n">
-        <v>0.9578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="657">
@@ -5685,7 +5685,7 @@
         <v>656</v>
       </c>
       <c r="B657" t="n">
-        <v>0</v>
+        <v>0.40515625</v>
       </c>
     </row>
     <row r="658">
@@ -5693,7 +5693,7 @@
         <v>657</v>
       </c>
       <c r="B658" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="659">
@@ -5701,7 +5701,7 @@
         <v>658</v>
       </c>
       <c r="B659" t="n">
-        <v>0.7553125000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="660">
@@ -5709,7 +5709,7 @@
         <v>659</v>
       </c>
       <c r="B660" t="n">
-        <v>0.69484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="661">
@@ -5725,7 +5725,7 @@
         <v>661</v>
       </c>
       <c r="B662" t="n">
-        <v>0.960625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="663">
@@ -5741,7 +5741,7 @@
         <v>663</v>
       </c>
       <c r="B664" t="n">
-        <v>0.6498437500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="665">
@@ -5757,7 +5757,7 @@
         <v>665</v>
       </c>
       <c r="B666" t="n">
-        <v>0.9465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="667">
@@ -5765,7 +5765,7 @@
         <v>666</v>
       </c>
       <c r="B667" t="n">
-        <v>0.8692187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="668">
@@ -5773,7 +5773,7 @@
         <v>667</v>
       </c>
       <c r="B668" t="n">
-        <v>0.75109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="669">
@@ -5781,7 +5781,7 @@
         <v>668</v>
       </c>
       <c r="B669" t="n">
-        <v>0.7876562499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="670">
@@ -5805,7 +5805,7 @@
         <v>671</v>
       </c>
       <c r="B672" t="n">
-        <v>0.8635937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="673">
@@ -5813,7 +5813,7 @@
         <v>672</v>
       </c>
       <c r="B673" t="n">
-        <v>0.90015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="674">
@@ -5821,7 +5821,7 @@
         <v>673</v>
       </c>
       <c r="B674" t="n">
-        <v>0.96203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="675">
@@ -5829,7 +5829,7 @@
         <v>674</v>
       </c>
       <c r="B675" t="n">
-        <v>0.96484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="676">
@@ -5837,7 +5837,7 @@
         <v>675</v>
       </c>
       <c r="B676" t="n">
-        <v>0.7834375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="677">
@@ -5893,7 +5893,7 @@
         <v>682</v>
       </c>
       <c r="B683" t="n">
-        <v>0.9578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="684">
@@ -5909,7 +5909,7 @@
         <v>684</v>
       </c>
       <c r="B685" t="n">
-        <v>0.499375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="686">
@@ -5917,7 +5917,7 @@
         <v>685</v>
       </c>
       <c r="B686" t="n">
-        <v>0.97609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="687">
@@ -5925,7 +5925,7 @@
         <v>686</v>
       </c>
       <c r="B687" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="688">
@@ -5933,7 +5933,7 @@
         <v>687</v>
       </c>
       <c r="B688" t="n">
-        <v>0.9339062499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="689">
@@ -5941,7 +5941,7 @@
         <v>688</v>
       </c>
       <c r="B689" t="n">
-        <v>0.63296875</v>
+        <v>0.31796875</v>
       </c>
     </row>
     <row r="690">
@@ -5973,7 +5973,7 @@
         <v>692</v>
       </c>
       <c r="B693" t="n">
-        <v>0.87625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="694">
@@ -5981,7 +5981,7 @@
         <v>693</v>
       </c>
       <c r="B694" t="n">
-        <v>0.8987499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="695">
@@ -5997,7 +5997,7 @@
         <v>695</v>
       </c>
       <c r="B696" t="n">
-        <v>0.5387500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="697">
@@ -6013,7 +6013,7 @@
         <v>697</v>
       </c>
       <c r="B698" t="n">
-        <v>0.9746875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="699">
@@ -6029,7 +6029,7 @@
         <v>699</v>
       </c>
       <c r="B700" t="n">
-        <v>0.55140625</v>
+        <v>0.12390625</v>
       </c>
     </row>
     <row r="701">
@@ -6037,2407 +6037,7 @@
         <v>700</v>
       </c>
       <c r="B701" t="n">
-        <v>0.88609375</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="n">
-        <v>701</v>
-      </c>
-      <c r="B702" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="n">
-        <v>702</v>
-      </c>
-      <c r="B703" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="n">
-        <v>703</v>
-      </c>
-      <c r="B704" t="n">
-        <v>0.7890625</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="n">
-        <v>704</v>
-      </c>
-      <c r="B705" t="n">
-        <v>0.960625</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="n">
-        <v>705</v>
-      </c>
-      <c r="B706" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="n">
-        <v>706</v>
-      </c>
-      <c r="B707" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="n">
-        <v>707</v>
-      </c>
-      <c r="B708" t="n">
-        <v>0.859375</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="n">
-        <v>708</v>
-      </c>
-      <c r="B709" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="n">
-        <v>709</v>
-      </c>
-      <c r="B710" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="n">
-        <v>710</v>
-      </c>
-      <c r="B711" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="n">
-        <v>711</v>
-      </c>
-      <c r="B712" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="n">
-        <v>712</v>
-      </c>
-      <c r="B713" t="n">
-        <v>0.6751562499999999</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="n">
-        <v>713</v>
-      </c>
-      <c r="B714" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="n">
-        <v>714</v>
-      </c>
-      <c r="B715" t="n">
-        <v>0.95359375</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="n">
-        <v>715</v>
-      </c>
-      <c r="B716" t="n">
-        <v>0.870625</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="n">
-        <v>716</v>
-      </c>
-      <c r="B717" t="n">
-        <v>0.926875</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="n">
-        <v>717</v>
-      </c>
-      <c r="B718" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="n">
-        <v>718</v>
-      </c>
-      <c r="B719" t="n">
-        <v>0.9803125</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="n">
-        <v>719</v>
-      </c>
-      <c r="B720" t="n">
-        <v>0.865</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="n">
-        <v>720</v>
-      </c>
-      <c r="B721" t="n">
-        <v>0.56125</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="n">
-        <v>721</v>
-      </c>
-      <c r="B722" t="n">
-        <v>0.8903125000000001</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="n">
-        <v>722</v>
-      </c>
-      <c r="B723" t="n">
-        <v>0.9240625</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="n">
-        <v>723</v>
-      </c>
-      <c r="B724" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="n">
-        <v>724</v>
-      </c>
-      <c r="B725" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="n">
-        <v>725</v>
-      </c>
-      <c r="B726" t="n">
-        <v>0.8931249999999999</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="n">
-        <v>726</v>
-      </c>
-      <c r="B727" t="n">
-        <v>0.955</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="n">
-        <v>727</v>
-      </c>
-      <c r="B728" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="n">
-        <v>728</v>
-      </c>
-      <c r="B729" t="n">
-        <v>0.92265625</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="n">
-        <v>729</v>
-      </c>
-      <c r="B730" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="n">
-        <v>730</v>
-      </c>
-      <c r="B731" t="n">
-        <v>0.9296875</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="n">
-        <v>731</v>
-      </c>
-      <c r="B732" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="n">
-        <v>732</v>
-      </c>
-      <c r="B733" t="n">
-        <v>0.95078125</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="n">
-        <v>733</v>
-      </c>
-      <c r="B734" t="n">
-        <v>0.88890625</v>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="n">
-        <v>734</v>
-      </c>
-      <c r="B735" t="n">
-        <v>0.6990625</v>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="n">
-        <v>735</v>
-      </c>
-      <c r="B736" t="n">
-        <v>0.2884375</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="n">
-        <v>736</v>
-      </c>
-      <c r="B737" t="n">
-        <v>0.94796875</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="n">
-        <v>737</v>
-      </c>
-      <c r="B738" t="n">
-        <v>0.7173437499999999</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="n">
-        <v>738</v>
-      </c>
-      <c r="B739" t="n">
-        <v>0.9859375</v>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="n">
-        <v>739</v>
-      </c>
-      <c r="B740" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="n">
-        <v>740</v>
-      </c>
-      <c r="B741" t="n">
-        <v>0.8115625</v>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="n">
-        <v>741</v>
-      </c>
-      <c r="B742" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="n">
-        <v>742</v>
-      </c>
-      <c r="B743" t="n">
-        <v>0.97328125</v>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="n">
-        <v>743</v>
-      </c>
-      <c r="B744" t="n">
-        <v>0.89171875</v>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="n">
-        <v>744</v>
-      </c>
-      <c r="B745" t="n">
-        <v>0.89734375</v>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="n">
-        <v>745</v>
-      </c>
-      <c r="B746" t="n">
-        <v>0.5921875</v>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="n">
-        <v>746</v>
-      </c>
-      <c r="B747" t="n">
-        <v>0.97046875</v>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="n">
-        <v>747</v>
-      </c>
-      <c r="B748" t="n">
-        <v>0.5021875</v>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="n">
-        <v>748</v>
-      </c>
-      <c r="B749" t="n">
-        <v>0.82703125</v>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="n">
-        <v>749</v>
-      </c>
-      <c r="B750" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="n">
-        <v>750</v>
-      </c>
-      <c r="B751" t="n">
-        <v>0.9409375</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="n">
-        <v>751</v>
-      </c>
-      <c r="B752" t="n">
-        <v>0.8509375</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="n">
-        <v>752</v>
-      </c>
-      <c r="B753" t="n">
-        <v>0.955</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="n">
-        <v>753</v>
-      </c>
-      <c r="B754" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="n">
-        <v>754</v>
-      </c>
-      <c r="B755" t="n">
-        <v>0.859375</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="n">
-        <v>755</v>
-      </c>
-      <c r="B756" t="n">
-        <v>0.285625</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="n">
-        <v>756</v>
-      </c>
-      <c r="B757" t="n">
-        <v>0.96203125</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="n">
-        <v>757</v>
-      </c>
-      <c r="B758" t="n">
-        <v>0.9746875</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="n">
-        <v>758</v>
-      </c>
-      <c r="B759" t="n">
-        <v>0.97328125</v>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="n">
-        <v>759</v>
-      </c>
-      <c r="B760" t="n">
-        <v>0.96203125</v>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="n">
-        <v>760</v>
-      </c>
-      <c r="B761" t="n">
-        <v>0.9339062499999999</v>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="n">
-        <v>761</v>
-      </c>
-      <c r="B762" t="n">
-        <v>0.2884375</v>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="n">
-        <v>762</v>
-      </c>
-      <c r="B763" t="n">
-        <v>0.9578125</v>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="n">
-        <v>763</v>
-      </c>
-      <c r="B764" t="n">
-        <v>0.701875</v>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="n">
-        <v>764</v>
-      </c>
-      <c r="B765" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="n">
-        <v>765</v>
-      </c>
-      <c r="B766" t="n">
-        <v>0.64140625</v>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="n">
-        <v>766</v>
-      </c>
-      <c r="B767" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" t="n">
-        <v>767</v>
-      </c>
-      <c r="B768" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" t="n">
-        <v>768</v>
-      </c>
-      <c r="B769" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" t="n">
-        <v>769</v>
-      </c>
-      <c r="B770" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" t="n">
-        <v>770</v>
-      </c>
-      <c r="B771" t="n">
-        <v>0.75109375</v>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" t="n">
-        <v>771</v>
-      </c>
-      <c r="B772" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="773">
-      <c r="A773" t="n">
-        <v>772</v>
-      </c>
-      <c r="B773" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" t="n">
-        <v>773</v>
-      </c>
-      <c r="B774" t="n">
-        <v>0.95078125</v>
-      </c>
-    </row>
-    <row r="775">
-      <c r="A775" t="n">
-        <v>774</v>
-      </c>
-      <c r="B775" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" t="n">
-        <v>775</v>
-      </c>
-      <c r="B776" t="n">
-        <v>0.97890625</v>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" t="n">
-        <v>776</v>
-      </c>
-      <c r="B777" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" t="n">
-        <v>777</v>
-      </c>
-      <c r="B778" t="n">
-        <v>0.9859375</v>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" t="n">
-        <v>778</v>
-      </c>
-      <c r="B779" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="n">
-        <v>779</v>
-      </c>
-      <c r="B780" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="n">
-        <v>780</v>
-      </c>
-      <c r="B781" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" t="n">
-        <v>781</v>
-      </c>
-      <c r="B782" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" t="n">
-        <v>782</v>
-      </c>
-      <c r="B783" t="n">
-        <v>0.84109375</v>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" t="n">
-        <v>783</v>
-      </c>
-      <c r="B784" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" t="n">
-        <v>784</v>
-      </c>
-      <c r="B785" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="n">
-        <v>785</v>
-      </c>
-      <c r="B786" t="n">
-        <v>0.7089062500000001</v>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" t="n">
-        <v>786</v>
-      </c>
-      <c r="B787" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="n">
-        <v>787</v>
-      </c>
-      <c r="B788" t="n">
-        <v>0.3503124999999999</v>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" t="n">
-        <v>788</v>
-      </c>
-      <c r="B789" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" t="n">
-        <v>789</v>
-      </c>
-      <c r="B790" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" t="n">
-        <v>790</v>
-      </c>
-      <c r="B791" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" t="n">
-        <v>791</v>
-      </c>
-      <c r="B792" t="n">
-        <v>0.1084375</v>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" t="n">
-        <v>792</v>
-      </c>
-      <c r="B793" t="n">
-        <v>0.3278125000000001</v>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="n">
-        <v>793</v>
-      </c>
-      <c r="B794" t="n">
-        <v>0.48390625</v>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" t="n">
-        <v>794</v>
-      </c>
-      <c r="B795" t="n">
-        <v>0.7384375</v>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" t="n">
-        <v>795</v>
-      </c>
-      <c r="B796" t="n">
-        <v>0.915625</v>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" t="n">
-        <v>796</v>
-      </c>
-      <c r="B797" t="n">
-        <v>0.48390625</v>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" t="n">
-        <v>797</v>
-      </c>
-      <c r="B798" t="n">
-        <v>0.87203125</v>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" t="n">
-        <v>798</v>
-      </c>
-      <c r="B799" t="n">
-        <v>0.8875</v>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" t="n">
-        <v>799</v>
-      </c>
-      <c r="B800" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" t="n">
-        <v>800</v>
-      </c>
-      <c r="B801" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" t="n">
-        <v>801</v>
-      </c>
-      <c r="B802" t="n">
-        <v>0.5696874999999999</v>
-      </c>
-    </row>
-    <row r="803">
-      <c r="A803" t="n">
-        <v>802</v>
-      </c>
-      <c r="B803" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="804">
-      <c r="A804" t="n">
-        <v>803</v>
-      </c>
-      <c r="B804" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="805">
-      <c r="A805" t="n">
-        <v>804</v>
-      </c>
-      <c r="B805" t="n">
-        <v>0.3095312499999999</v>
-      </c>
-    </row>
-    <row r="806">
-      <c r="A806" t="n">
-        <v>805</v>
-      </c>
-      <c r="B806" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="807">
-      <c r="A807" t="n">
-        <v>806</v>
-      </c>
-      <c r="B807" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="808">
-      <c r="A808" t="n">
-        <v>807</v>
-      </c>
-      <c r="B808" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" t="n">
-        <v>808</v>
-      </c>
-      <c r="B809" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" t="n">
-        <v>809</v>
-      </c>
-      <c r="B810" t="n">
-        <v>0.61328125</v>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" t="n">
-        <v>810</v>
-      </c>
-      <c r="B811" t="n">
-        <v>0.4149999999999999</v>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" t="n">
-        <v>811</v>
-      </c>
-      <c r="B812" t="n">
-        <v>0.499375</v>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" t="n">
-        <v>812</v>
-      </c>
-      <c r="B813" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" t="n">
-        <v>813</v>
-      </c>
-      <c r="B814" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" t="n">
-        <v>814</v>
-      </c>
-      <c r="B815" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="816">
-      <c r="A816" t="n">
-        <v>815</v>
-      </c>
-      <c r="B816" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" t="n">
-        <v>816</v>
-      </c>
-      <c r="B817" t="n">
-        <v>0.8059375</v>
-      </c>
-    </row>
-    <row r="818">
-      <c r="A818" t="n">
-        <v>817</v>
-      </c>
-      <c r="B818" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="819">
-      <c r="A819" t="n">
-        <v>818</v>
-      </c>
-      <c r="B819" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" t="n">
-        <v>819</v>
-      </c>
-      <c r="B820" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" t="n">
-        <v>820</v>
-      </c>
-      <c r="B821" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" t="n">
-        <v>821</v>
-      </c>
-      <c r="B822" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" t="n">
-        <v>822</v>
-      </c>
-      <c r="B823" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="824">
-      <c r="A824" t="n">
-        <v>823</v>
-      </c>
-      <c r="B824" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="825">
-      <c r="A825" t="n">
-        <v>824</v>
-      </c>
-      <c r="B825" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="826">
-      <c r="A826" t="n">
-        <v>825</v>
-      </c>
-      <c r="B826" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="827">
-      <c r="A827" t="n">
-        <v>826</v>
-      </c>
-      <c r="B827" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="828">
-      <c r="A828" t="n">
-        <v>827</v>
-      </c>
-      <c r="B828" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" t="n">
-        <v>828</v>
-      </c>
-      <c r="B829" t="n">
-        <v>0.48953125</v>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" t="n">
-        <v>829</v>
-      </c>
-      <c r="B830" t="n">
-        <v>0.6090625000000001</v>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" t="n">
-        <v>830</v>
-      </c>
-      <c r="B831" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" t="n">
-        <v>831</v>
-      </c>
-      <c r="B832" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" t="n">
-        <v>832</v>
-      </c>
-      <c r="B833" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="834">
-      <c r="A834" t="n">
-        <v>833</v>
-      </c>
-      <c r="B834" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" t="n">
-        <v>834</v>
-      </c>
-      <c r="B835" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="836">
-      <c r="A836" t="n">
-        <v>835</v>
-      </c>
-      <c r="B836" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" t="n">
-        <v>836</v>
-      </c>
-      <c r="B837" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="838">
-      <c r="A838" t="n">
-        <v>837</v>
-      </c>
-      <c r="B838" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" t="n">
-        <v>838</v>
-      </c>
-      <c r="B839" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="840">
-      <c r="A840" t="n">
-        <v>839</v>
-      </c>
-      <c r="B840" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="841">
-      <c r="A841" t="n">
-        <v>840</v>
-      </c>
-      <c r="B841" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="842">
-      <c r="A842" t="n">
-        <v>841</v>
-      </c>
-      <c r="B842" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="843">
-      <c r="A843" t="n">
-        <v>842</v>
-      </c>
-      <c r="B843" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="844">
-      <c r="A844" t="n">
-        <v>843</v>
-      </c>
-      <c r="B844" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="845">
-      <c r="A845" t="n">
-        <v>844</v>
-      </c>
-      <c r="B845" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="846">
-      <c r="A846" t="n">
-        <v>845</v>
-      </c>
-      <c r="B846" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="847">
-      <c r="A847" t="n">
-        <v>846</v>
-      </c>
-      <c r="B847" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="848">
-      <c r="A848" t="n">
-        <v>847</v>
-      </c>
-      <c r="B848" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="849">
-      <c r="A849" t="n">
-        <v>848</v>
-      </c>
-      <c r="B849" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="850">
-      <c r="A850" t="n">
-        <v>849</v>
-      </c>
-      <c r="B850" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="851">
-      <c r="A851" t="n">
-        <v>850</v>
-      </c>
-      <c r="B851" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="852">
-      <c r="A852" t="n">
-        <v>851</v>
-      </c>
-      <c r="B852" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="853">
-      <c r="A853" t="n">
-        <v>852</v>
-      </c>
-      <c r="B853" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="854">
-      <c r="A854" t="n">
-        <v>853</v>
-      </c>
-      <c r="B854" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="855">
-      <c r="A855" t="n">
-        <v>854</v>
-      </c>
-      <c r="B855" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="856">
-      <c r="A856" t="n">
-        <v>855</v>
-      </c>
-      <c r="B856" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="857">
-      <c r="A857" t="n">
-        <v>856</v>
-      </c>
-      <c r="B857" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="858">
-      <c r="A858" t="n">
-        <v>857</v>
-      </c>
-      <c r="B858" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="859">
-      <c r="A859" t="n">
-        <v>858</v>
-      </c>
-      <c r="B859" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="860">
-      <c r="A860" t="n">
-        <v>859</v>
-      </c>
-      <c r="B860" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="861">
-      <c r="A861" t="n">
-        <v>860</v>
-      </c>
-      <c r="B861" t="n">
-        <v>0.4459375</v>
-      </c>
-    </row>
-    <row r="862">
-      <c r="A862" t="n">
-        <v>861</v>
-      </c>
-      <c r="B862" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="863">
-      <c r="A863" t="n">
-        <v>862</v>
-      </c>
-      <c r="B863" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="864">
-      <c r="A864" t="n">
-        <v>863</v>
-      </c>
-      <c r="B864" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="865">
-      <c r="A865" t="n">
-        <v>864</v>
-      </c>
-      <c r="B865" t="n">
-        <v>0.521875</v>
-      </c>
-    </row>
-    <row r="866">
-      <c r="A866" t="n">
-        <v>865</v>
-      </c>
-      <c r="B866" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="867">
-      <c r="A867" t="n">
-        <v>866</v>
-      </c>
-      <c r="B867" t="n">
-        <v>0.2954687499999999</v>
-      </c>
-    </row>
-    <row r="868">
-      <c r="A868" t="n">
-        <v>867</v>
-      </c>
-      <c r="B868" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" t="n">
-        <v>868</v>
-      </c>
-      <c r="B869" t="n">
-        <v>0.48671875</v>
-      </c>
-    </row>
-    <row r="870">
-      <c r="A870" t="n">
-        <v>869</v>
-      </c>
-      <c r="B870" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="871">
-      <c r="A871" t="n">
-        <v>870</v>
-      </c>
-      <c r="B871" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="872">
-      <c r="A872" t="n">
-        <v>871</v>
-      </c>
-      <c r="B872" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="873">
-      <c r="A873" t="n">
-        <v>872</v>
-      </c>
-      <c r="B873" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="874">
-      <c r="A874" t="n">
-        <v>873</v>
-      </c>
-      <c r="B874" t="n">
-        <v>0.6034375000000001</v>
-      </c>
-    </row>
-    <row r="875">
-      <c r="A875" t="n">
-        <v>874</v>
-      </c>
-      <c r="B875" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="876">
-      <c r="A876" t="n">
-        <v>875</v>
-      </c>
-      <c r="B876" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="877">
-      <c r="A877" t="n">
-        <v>876</v>
-      </c>
-      <c r="B877" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" t="n">
-        <v>877</v>
-      </c>
-      <c r="B878" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="879">
-      <c r="A879" t="n">
-        <v>878</v>
-      </c>
-      <c r="B879" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="880">
-      <c r="A880" t="n">
-        <v>879</v>
-      </c>
-      <c r="B880" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="881">
-      <c r="A881" t="n">
-        <v>880</v>
-      </c>
-      <c r="B881" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="882">
-      <c r="A882" t="n">
-        <v>881</v>
-      </c>
-      <c r="B882" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="883">
-      <c r="A883" t="n">
-        <v>882</v>
-      </c>
-      <c r="B883" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="884">
-      <c r="A884" t="n">
-        <v>883</v>
-      </c>
-      <c r="B884" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" t="n">
-        <v>884</v>
-      </c>
-      <c r="B885" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="886">
-      <c r="A886" t="n">
-        <v>885</v>
-      </c>
-      <c r="B886" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="887">
-      <c r="A887" t="n">
-        <v>886</v>
-      </c>
-      <c r="B887" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="888">
-      <c r="A888" t="n">
-        <v>887</v>
-      </c>
-      <c r="B888" t="n">
-        <v>0.308125</v>
-      </c>
-    </row>
-    <row r="889">
-      <c r="A889" t="n">
-        <v>888</v>
-      </c>
-      <c r="B889" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="890">
-      <c r="A890" t="n">
-        <v>889</v>
-      </c>
-      <c r="B890" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="891">
-      <c r="A891" t="n">
-        <v>890</v>
-      </c>
-      <c r="B891" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="892">
-      <c r="A892" t="n">
-        <v>891</v>
-      </c>
-      <c r="B892" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="893">
-      <c r="A893" t="n">
-        <v>892</v>
-      </c>
-      <c r="B893" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="894">
-      <c r="A894" t="n">
-        <v>893</v>
-      </c>
-      <c r="B894" t="n">
-        <v>0.6484375</v>
-      </c>
-    </row>
-    <row r="895">
-      <c r="A895" t="n">
-        <v>894</v>
-      </c>
-      <c r="B895" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="896">
-      <c r="A896" t="n">
-        <v>895</v>
-      </c>
-      <c r="B896" t="n">
-        <v>0.8579687499999999</v>
-      </c>
-    </row>
-    <row r="897">
-      <c r="A897" t="n">
-        <v>896</v>
-      </c>
-      <c r="B897" t="n">
-        <v>0.62171875</v>
-      </c>
-    </row>
-    <row r="898">
-      <c r="A898" t="n">
-        <v>897</v>
-      </c>
-      <c r="B898" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="899">
-      <c r="A899" t="n">
-        <v>898</v>
-      </c>
-      <c r="B899" t="n">
-        <v>0.713125</v>
-      </c>
-    </row>
-    <row r="900">
-      <c r="A900" t="n">
-        <v>899</v>
-      </c>
-      <c r="B900" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="901">
-      <c r="A901" t="n">
-        <v>900</v>
-      </c>
-      <c r="B901" t="n">
-        <v>0.859375</v>
-      </c>
-    </row>
-    <row r="902">
-      <c r="A902" t="n">
-        <v>901</v>
-      </c>
-      <c r="B902" t="n">
-        <v>0.84671875</v>
-      </c>
-    </row>
-    <row r="903">
-      <c r="A903" t="n">
-        <v>902</v>
-      </c>
-      <c r="B903" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="904">
-      <c r="A904" t="n">
-        <v>903</v>
-      </c>
-      <c r="B904" t="n">
-        <v>0.4360937499999999</v>
-      </c>
-    </row>
-    <row r="905">
-      <c r="A905" t="n">
-        <v>904</v>
-      </c>
-      <c r="B905" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="906">
-      <c r="A906" t="n">
-        <v>905</v>
-      </c>
-      <c r="B906" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="907">
-      <c r="A907" t="n">
-        <v>906</v>
-      </c>
-      <c r="B907" t="n">
-        <v>0.2715625</v>
-      </c>
-    </row>
-    <row r="908">
-      <c r="A908" t="n">
-        <v>907</v>
-      </c>
-      <c r="B908" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="909">
-      <c r="A909" t="n">
-        <v>908</v>
-      </c>
-      <c r="B909" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="910">
-      <c r="A910" t="n">
-        <v>909</v>
-      </c>
-      <c r="B910" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="911">
-      <c r="A911" t="n">
-        <v>910</v>
-      </c>
-      <c r="B911" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="912">
-      <c r="A912" t="n">
-        <v>911</v>
-      </c>
-      <c r="B912" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="913">
-      <c r="A913" t="n">
-        <v>912</v>
-      </c>
-      <c r="B913" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="914">
-      <c r="A914" t="n">
-        <v>913</v>
-      </c>
-      <c r="B914" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="915">
-      <c r="A915" t="n">
-        <v>914</v>
-      </c>
-      <c r="B915" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="916">
-      <c r="A916" t="n">
-        <v>915</v>
-      </c>
-      <c r="B916" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="917">
-      <c r="A917" t="n">
-        <v>916</v>
-      </c>
-      <c r="B917" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="918">
-      <c r="A918" t="n">
-        <v>917</v>
-      </c>
-      <c r="B918" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="919">
-      <c r="A919" t="n">
-        <v>918</v>
-      </c>
-      <c r="B919" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="920">
-      <c r="A920" t="n">
-        <v>919</v>
-      </c>
-      <c r="B920" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="921">
-      <c r="A921" t="n">
-        <v>920</v>
-      </c>
-      <c r="B921" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="922">
-      <c r="A922" t="n">
-        <v>921</v>
-      </c>
-      <c r="B922" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="923">
-      <c r="A923" t="n">
-        <v>922</v>
-      </c>
-      <c r="B923" t="n">
-        <v>0.3714062499999999</v>
-      </c>
-    </row>
-    <row r="924">
-      <c r="A924" t="n">
-        <v>923</v>
-      </c>
-      <c r="B924" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="925">
-      <c r="A925" t="n">
-        <v>924</v>
-      </c>
-      <c r="B925" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="926">
-      <c r="A926" t="n">
-        <v>925</v>
-      </c>
-      <c r="B926" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="927">
-      <c r="A927" t="n">
-        <v>926</v>
-      </c>
-      <c r="B927" t="n">
-        <v>0.73421875</v>
-      </c>
-    </row>
-    <row r="928">
-      <c r="A928" t="n">
-        <v>927</v>
-      </c>
-      <c r="B928" t="n">
-        <v>0.58375</v>
-      </c>
-    </row>
-    <row r="929">
-      <c r="A929" t="n">
-        <v>928</v>
-      </c>
-      <c r="B929" t="n">
-        <v>0.2307812499999999</v>
-      </c>
-    </row>
-    <row r="930">
-      <c r="A930" t="n">
-        <v>929</v>
-      </c>
-      <c r="B930" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="931">
-      <c r="A931" t="n">
-        <v>930</v>
-      </c>
-      <c r="B931" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="932">
-      <c r="A932" t="n">
-        <v>931</v>
-      </c>
-      <c r="B932" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="933">
-      <c r="A933" t="n">
-        <v>932</v>
-      </c>
-      <c r="B933" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="934">
-      <c r="A934" t="n">
-        <v>933</v>
-      </c>
-      <c r="B934" t="n">
-        <v>0.7159375</v>
-      </c>
-    </row>
-    <row r="935">
-      <c r="A935" t="n">
-        <v>934</v>
-      </c>
-      <c r="B935" t="n">
-        <v>0.81578125</v>
-      </c>
-    </row>
-    <row r="936">
-      <c r="A936" t="n">
-        <v>935</v>
-      </c>
-      <c r="B936" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="937">
-      <c r="A937" t="n">
-        <v>936</v>
-      </c>
-      <c r="B937" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="938">
-      <c r="A938" t="n">
-        <v>937</v>
-      </c>
-      <c r="B938" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="939">
-      <c r="A939" t="n">
-        <v>938</v>
-      </c>
-      <c r="B939" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="940">
-      <c r="A940" t="n">
-        <v>939</v>
-      </c>
-      <c r="B940" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="941">
-      <c r="A941" t="n">
-        <v>940</v>
-      </c>
-      <c r="B941" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="942">
-      <c r="A942" t="n">
-        <v>941</v>
-      </c>
-      <c r="B942" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="943">
-      <c r="A943" t="n">
-        <v>942</v>
-      </c>
-      <c r="B943" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="944">
-      <c r="A944" t="n">
-        <v>943</v>
-      </c>
-      <c r="B944" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="945">
-      <c r="A945" t="n">
-        <v>944</v>
-      </c>
-      <c r="B945" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="946">
-      <c r="A946" t="n">
-        <v>945</v>
-      </c>
-      <c r="B946" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="947">
-      <c r="A947" t="n">
-        <v>946</v>
-      </c>
-      <c r="B947" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="948">
-      <c r="A948" t="n">
-        <v>947</v>
-      </c>
-      <c r="B948" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="949">
-      <c r="A949" t="n">
-        <v>948</v>
-      </c>
-      <c r="B949" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="950">
-      <c r="A950" t="n">
-        <v>949</v>
-      </c>
-      <c r="B950" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="951">
-      <c r="A951" t="n">
-        <v>950</v>
-      </c>
-      <c r="B951" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="952">
-      <c r="A952" t="n">
-        <v>951</v>
-      </c>
-      <c r="B952" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="953">
-      <c r="A953" t="n">
-        <v>952</v>
-      </c>
-      <c r="B953" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="954">
-      <c r="A954" t="n">
-        <v>953</v>
-      </c>
-      <c r="B954" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="955">
-      <c r="A955" t="n">
-        <v>954</v>
-      </c>
-      <c r="B955" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="956">
-      <c r="A956" t="n">
-        <v>955</v>
-      </c>
-      <c r="B956" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="957">
-      <c r="A957" t="n">
-        <v>956</v>
-      </c>
-      <c r="B957" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="958">
-      <c r="A958" t="n">
-        <v>957</v>
-      </c>
-      <c r="B958" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="959">
-      <c r="A959" t="n">
-        <v>958</v>
-      </c>
-      <c r="B959" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="960">
-      <c r="A960" t="n">
-        <v>959</v>
-      </c>
-      <c r="B960" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="961">
-      <c r="A961" t="n">
-        <v>960</v>
-      </c>
-      <c r="B961" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="962">
-      <c r="A962" t="n">
-        <v>961</v>
-      </c>
-      <c r="B962" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="963">
-      <c r="A963" t="n">
-        <v>962</v>
-      </c>
-      <c r="B963" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="964">
-      <c r="A964" t="n">
-        <v>963</v>
-      </c>
-      <c r="B964" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="965">
-      <c r="A965" t="n">
-        <v>964</v>
-      </c>
-      <c r="B965" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="966">
-      <c r="A966" t="n">
-        <v>965</v>
-      </c>
-      <c r="B966" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="967">
-      <c r="A967" t="n">
-        <v>966</v>
-      </c>
-      <c r="B967" t="n">
-        <v>0.5078125</v>
-      </c>
-    </row>
-    <row r="968">
-      <c r="A968" t="n">
-        <v>967</v>
-      </c>
-      <c r="B968" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="969">
-      <c r="A969" t="n">
-        <v>968</v>
-      </c>
-      <c r="B969" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="970">
-      <c r="A970" t="n">
-        <v>969</v>
-      </c>
-      <c r="B970" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="971">
-      <c r="A971" t="n">
-        <v>970</v>
-      </c>
-      <c r="B971" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="972">
-      <c r="A972" t="n">
-        <v>971</v>
-      </c>
-      <c r="B972" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="973">
-      <c r="A973" t="n">
-        <v>972</v>
-      </c>
-      <c r="B973" t="n">
-        <v>0.1590625</v>
-      </c>
-    </row>
-    <row r="974">
-      <c r="A974" t="n">
-        <v>973</v>
-      </c>
-      <c r="B974" t="n">
-        <v>0.25046875</v>
-      </c>
-    </row>
-    <row r="975">
-      <c r="A975" t="n">
-        <v>974</v>
-      </c>
-      <c r="B975" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="976">
-      <c r="A976" t="n">
-        <v>975</v>
-      </c>
-      <c r="B976" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="977">
-      <c r="A977" t="n">
-        <v>976</v>
-      </c>
-      <c r="B977" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="978">
-      <c r="A978" t="n">
-        <v>977</v>
-      </c>
-      <c r="B978" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="979">
-      <c r="A979" t="n">
-        <v>978</v>
-      </c>
-      <c r="B979" t="n">
-        <v>0.1520312500000001</v>
-      </c>
-    </row>
-    <row r="980">
-      <c r="A980" t="n">
-        <v>979</v>
-      </c>
-      <c r="B980" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="981">
-      <c r="A981" t="n">
-        <v>980</v>
-      </c>
-      <c r="B981" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="982">
-      <c r="A982" t="n">
-        <v>981</v>
-      </c>
-      <c r="B982" t="n">
-        <v>0.6695312499999999</v>
-      </c>
-    </row>
-    <row r="983">
-      <c r="A983" t="n">
-        <v>982</v>
-      </c>
-      <c r="B983" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="984">
-      <c r="A984" t="n">
-        <v>983</v>
-      </c>
-      <c r="B984" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="985">
-      <c r="A985" t="n">
-        <v>984</v>
-      </c>
-      <c r="B985" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="986">
-      <c r="A986" t="n">
-        <v>985</v>
-      </c>
-      <c r="B986" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="987">
-      <c r="A987" t="n">
-        <v>986</v>
-      </c>
-      <c r="B987" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="988">
-      <c r="A988" t="n">
-        <v>987</v>
-      </c>
-      <c r="B988" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="989">
-      <c r="A989" t="n">
-        <v>988</v>
-      </c>
-      <c r="B989" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="990">
-      <c r="A990" t="n">
-        <v>989</v>
-      </c>
-      <c r="B990" t="n">
-        <v>0.521875</v>
-      </c>
-    </row>
-    <row r="991">
-      <c r="A991" t="n">
-        <v>990</v>
-      </c>
-      <c r="B991" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="992">
-      <c r="A992" t="n">
-        <v>991</v>
-      </c>
-      <c r="B992" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="993">
-      <c r="A993" t="n">
-        <v>992</v>
-      </c>
-      <c r="B993" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="994">
-      <c r="A994" t="n">
-        <v>993</v>
-      </c>
-      <c r="B994" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="995">
-      <c r="A995" t="n">
-        <v>994</v>
-      </c>
-      <c r="B995" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="996">
-      <c r="A996" t="n">
-        <v>995</v>
-      </c>
-      <c r="B996" t="n">
-        <v>0.60203125</v>
-      </c>
-    </row>
-    <row r="997">
-      <c r="A997" t="n">
-        <v>996</v>
-      </c>
-      <c r="B997" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="998">
-      <c r="A998" t="n">
-        <v>997</v>
-      </c>
-      <c r="B998" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="999">
-      <c r="A999" t="n">
-        <v>998</v>
-      </c>
-      <c r="B999" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1000">
-      <c r="A1000" t="n">
-        <v>999</v>
-      </c>
-      <c r="B1000" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1001">
-      <c r="A1001" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B1001" t="n">
-        <v>0</v>
+        <v>0.375625</v>
       </c>
     </row>
   </sheetData>
